--- a/src/test/resources/codechgfile.text.xlsx
+++ b/src/test/resources/codechgfile.text.xlsx
@@ -34,7 +34,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J125"/>
+  <dimension ref="A1:J134"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -96,42 +96,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0030274</t>
+          <t xml:space="preserve">0070182</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">기업　　　　　　　　</t>
+          <t xml:space="preserve">수협은행　　　　　　</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성수동（지）　　　　　　　　　</t>
+          <t xml:space="preserve">여신관리센터　　　　　　　　　</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   499  8001 </t>
+          <t xml:space="preserve">02   6055 7877 </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 075  0027 </t>
+          <t xml:space="preserve">02   418  7771 </t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04782 </t>
+          <t xml:space="preserve">05542 </t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260622</t>
+          <t xml:space="preserve">20260624</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　성동구　광나루로６길　１４　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　송파구　올림픽로　３４０　５층（방이동　대동빌딩）　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -143,47 +143,47 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0113874</t>
+          <t xml:space="preserve">0324003</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
+          <t xml:space="preserve">부산　　　　　　　　</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">작전동　　　　　　　　　　　　</t>
+          <t xml:space="preserve">복합지원센터　　　　　　　　　</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">032  552  4121 </t>
+          <t xml:space="preserve">051  248  3967 </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">032  552  0437 </t>
+          <t xml:space="preserve">051  608  5240 </t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21120 </t>
+          <t xml:space="preserve">48955 </t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260622</t>
+          <t xml:space="preserve">20260623</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">인천광역시　계양구　계양대로　４０　（작전동），　１층　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">부산광역시　중구　중앙대로　２１　（중앙동６가）　부산데파트　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -200,42 +200,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0203881</t>
+          <t xml:space="preserve">0472900</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">우리은행　　　　　　</t>
+          <t xml:space="preserve">신협　　　　　　　　</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">인하스카이지점　　　　　　　　</t>
+          <t xml:space="preserve">제주신협　동문지점　　　　　　</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">032  831  6321 </t>
+          <t xml:space="preserve">064  752  5101 </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 001  3388 </t>
+          <t xml:space="preserve">064  758  0589 </t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">22188 </t>
+          <t xml:space="preserve">63264 </t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260622</t>
+          <t xml:space="preserve">20260623</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">인천광역시　미추홀구　용정공원로８３번길　５９　（용현동）　３층　３０２호　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">제주특별자치도　제주시　동문로　４　（일도일동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -247,156 +247,156 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">0231277</t>
+          <t xml:space="preserve">0487584</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＳＣ제일　　　　　　</t>
+          <t xml:space="preserve">신협　　　　　　　　</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">장사동（지）　　　　　　　　　</t>
+          <t xml:space="preserve">청주드림신협　문화센터지점　　</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2265 4101 </t>
+          <t xml:space="preserve">043  233  8100 </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2278 9793 </t>
+          <t xml:space="preserve">043  233  8103 </t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">110430</t>
+          <t xml:space="preserve">28362 </t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260622</t>
+          <t xml:space="preserve">20260623</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울　종로구　장사동　２０７의１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">충청북도　청주시　흥덕구　２순환로　１０９８　（비하동）　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">0231086</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">0232807</t>
+          <t xml:space="preserve">0494988</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＳＣ제일　　　　　　</t>
+          <t xml:space="preserve">신협　　　　　　　　</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">남가좌동（지）　　　　　　　　</t>
+          <t xml:space="preserve">제주신협　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   304  1091 </t>
+          <t xml:space="preserve">064  721  5101 </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   308  7452 </t>
+          <t xml:space="preserve">0505 081  1013 </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">03670 </t>
+          <t xml:space="preserve">63234 </t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260622</t>
+          <t xml:space="preserve">20260623</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울　서대문구　증가로１５０　ＤＭＣ　아이파크아파트상가２층　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">제주특별자치도　제주시　연북로　５１７　（아라일동）　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">0232784</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">0235037</t>
+          <t xml:space="preserve">0497257</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＳＣ제일　　　　　　</t>
+          <t xml:space="preserve">신협　　　　　　　　</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">범일동（지）　　　　　　　　　</t>
+          <t xml:space="preserve">제주신협　일도지점　　　　　　</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">051  646  5173 </t>
+          <t xml:space="preserve">064  752  5102 </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">051  643  7732 </t>
+          <t xml:space="preserve">064  752  8388 </t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">48738 </t>
+          <t xml:space="preserve">63275 </t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260622</t>
+          <t xml:space="preserve">20260623</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">부산광역시　동구　조방로　３９　２층　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">제주특별자치도　제주시　고마로　１０４　（일도이동）　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">0235040</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
@@ -408,42 +408,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0235040</t>
+          <t xml:space="preserve">0860907</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＳＣ제일　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">부산서면ＷＭ센터　　　　　　　</t>
+          <t xml:space="preserve">명동금고시청역지점　　　　　　</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">051  802  5321 </t>
+          <t xml:space="preserve">02   755  0038 </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">051  816  0401 </t>
+          <t xml:space="preserve">02   778  1980 </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">47245 </t>
+          <t xml:space="preserve">04526 </t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260622</t>
+          <t xml:space="preserve">20260623</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">부산광역시　부산진구　중앙대로　７３６　（부전동）　경암센터　１층　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　중구　세종대로　８４　（태평로２가）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -460,42 +460,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">0805072</t>
+          <t xml:space="preserve">0872788</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나　　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">한겨레（출）　　　　　　　　　</t>
+          <t xml:space="preserve">대연금고　남광지점　　　　　　</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   703  1111 </t>
+          <t xml:space="preserve">051  624  5800 </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   704  9199 </t>
+          <t xml:space="preserve">051  714  0108 </t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">04186 </t>
+          <t xml:space="preserve">48532 </t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260622</t>
+          <t xml:space="preserve">20260623</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울　마포구　효창목길　６　（공덕동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">부산시　남구　흥곡로　３６０　대연금고　남광지점　상가　４０２동　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -507,47 +507,47 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">0156679</t>
+          <t xml:space="preserve">0877754</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">태안　반월　　　　　　　　　　</t>
+          <t xml:space="preserve">경산금고　정평역지점　　　　　</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  273  7859 </t>
+          <t xml:space="preserve">053  716  7517 </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  273  7863 </t>
+          <t xml:space="preserve">053  716  7518 </t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">18380 </t>
+          <t xml:space="preserve">38653 </t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260619</t>
+          <t xml:space="preserve">20260623</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　화성시　병점구　영통로　１４－１０　１０５호（반월동，토마토프라자）　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상북도　경산시　성동로　２　（정평동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -564,42 +564,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">0734062</t>
+          <t xml:space="preserve">0030274</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">우체국　　　　　　　</t>
+          <t xml:space="preserve">기업　　　　　　　　</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">홍성우체국　　　　　　　　　　</t>
+          <t xml:space="preserve">성수동（지）　　　　　　　　　</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">041  632  2014 </t>
+          <t xml:space="preserve">02   499  8001 </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">041  633  2006 </t>
+          <t xml:space="preserve">0505 075  0027 </t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">32247 </t>
+          <t xml:space="preserve">04782 </t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260619</t>
+          <t xml:space="preserve">20260622</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">충청남도　홍성군　홍성읍　내포로　１１１　（홍성읍，홍성우체국）　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　성동구　광나루로６길　１４　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -616,42 +616,42 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">0746623</t>
+          <t xml:space="preserve">0113874</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">우체국　　　　　　　</t>
+          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">광주오치동우체국　　　　　　　</t>
+          <t xml:space="preserve">작전동　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">062  264  2704 </t>
+          <t xml:space="preserve">032  552  4121 </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">062  267  1375 </t>
+          <t xml:space="preserve">032  552  0437 </t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">61122 </t>
+          <t xml:space="preserve">21120 </t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260619</t>
+          <t xml:space="preserve">20260622</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">광주광역시　북구　서하로　２４１　（오치동，오치동우체국）　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">인천광역시　계양구　계양대로　４０　（작전동），　１층　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -668,42 +668,42 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">0748333</t>
+          <t xml:space="preserve">0203881</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">우체국　　　　　　　</t>
+          <t xml:space="preserve">우리은행　　　　　　</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">금융원２지급센터　　　　　　　</t>
+          <t xml:space="preserve">인하스카이지점　　　　　　　　</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">062  375  7430 </t>
+          <t xml:space="preserve">032  831  6321 </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">               </t>
+          <t xml:space="preserve">0505 001  3388 </t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">61947 </t>
+          <t xml:space="preserve">22188 </t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260619</t>
+          <t xml:space="preserve">20260622</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">광주광역시　서구　상무중앙로　１１０　（치평동，우체국보험광주회관）　４층　청구심사２팀　　　　　　</t>
+          <t xml:space="preserve">인천광역시　미추홀구　용정공원로８３번길　５９　（용현동）　３층　３０２호　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -715,104 +715,104 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">4920021</t>
+          <t xml:space="preserve">0231277</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">중소벤처기업진흥공단</t>
+          <t xml:space="preserve">ＳＣ제일　　　　　　</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">본사　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">장사동（지）　　　　　　　　　</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  751  9607 </t>
+          <t xml:space="preserve">02   2265 4101 </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 047  4414 </t>
+          <t xml:space="preserve">02   2278 9793 </t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">52851 </t>
+          <t xml:space="preserve">110430</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260619</t>
+          <t xml:space="preserve">20260622</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　동진로　４３０　（충무공동）　대출관리실　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울　종로구　장사동　２０７의１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0231086</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">잠정패쇄</t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">0183176</t>
+          <t xml:space="preserve">0232807</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">ＳＣ제일　　　　　　</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">일산　풍산역　　　　　　　　　</t>
+          <t xml:space="preserve">남가좌동（지）　　　　　　　　</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  977  8062 </t>
+          <t xml:space="preserve">02   304  1091 </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  977  8063 </t>
+          <t xml:space="preserve">02   308  7452 </t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">10355 </t>
+          <t xml:space="preserve">03670 </t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260618</t>
+          <t xml:space="preserve">20260622</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　고양시　일산동구　중산로　６３　현대프라자　２０１호　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울　서대문구　증가로１５０　ＤＭＣ　아이파크아파트상가２층　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve">0122409</t>
+          <t xml:space="preserve">0232784</t>
         </is>
       </c>
     </row>
@@ -824,47 +824,47 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">0390231</t>
+          <t xml:space="preserve">0235037</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">경남　　　　　　　　</t>
+          <t xml:space="preserve">ＳＣ제일　　　　　　</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">통합제도부　　　　　　　　　　</t>
+          <t xml:space="preserve">범일동（지）　　　　　　　　　</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  290  8381 </t>
+          <t xml:space="preserve">051  646  5173 </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 082  6067 </t>
+          <t xml:space="preserve">051  643  7732 </t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">51316 </t>
+          <t xml:space="preserve">48738 </t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260618</t>
+          <t xml:space="preserve">20260622</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　창원시　마산회원구　３·１５대로　６４２　（석전동）　６４２　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">부산광역시　동구　조방로　３９　２층　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve">0390671</t>
+          <t xml:space="preserve">0235040</t>
         </is>
       </c>
     </row>
@@ -876,42 +876,42 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">0390532</t>
+          <t xml:space="preserve">0235040</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">경남　　　　　　　　</t>
+          <t xml:space="preserve">ＳＣ제일　　　　　　</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">디지털전략부　　　　　　　　　</t>
+          <t xml:space="preserve">부산서면ＷＭ센터　　　　　　　</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  290  8000 </t>
+          <t xml:space="preserve">051  802  5321 </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  290  8993 </t>
+          <t xml:space="preserve">051  816  0401 </t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">630807</t>
+          <t xml:space="preserve">47245 </t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260618</t>
+          <t xml:space="preserve">20260622</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　창원시　마산회원구　３·１５대로　６４２　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">부산광역시　부산진구　중앙대로　７３６　（부전동）　경암센터　１층　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -928,42 +928,42 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">0390862</t>
+          <t xml:space="preserve">0805072</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">경남　　　　　　　　</t>
+          <t xml:space="preserve">하나　　　　　　　　</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">비대면마케팅부　　　　　　　　</t>
+          <t xml:space="preserve">한겨레（출）　　　　　　　　　</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  290  8000 </t>
+          <t xml:space="preserve">02   703  1111 </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  290  8000 </t>
+          <t xml:space="preserve">02   704  9199 </t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">51316 </t>
+          <t xml:space="preserve">04186 </t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260618</t>
+          <t xml:space="preserve">20260622</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　창원시　마산회원구　３·１５대로　６４２（석전동）　디지털마케팅부　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울　마포구　효창목길　６　（공덕동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -975,52 +975,52 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">0391942</t>
+          <t xml:space="preserve">0156679</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">경남　　　　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">윤리경영부　　　　　　　　　　</t>
+          <t xml:space="preserve">태안　반월　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  1588 8585 </t>
+          <t xml:space="preserve">031  273  7859 </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 082  5300 </t>
+          <t xml:space="preserve">031  273  7863 </t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">51316 </t>
+          <t xml:space="preserve">18380 </t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260618</t>
+          <t xml:space="preserve">20260619</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　창원시　마산회원구　３·１５대로　６４２　（석전동）　윤리경영부　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　화성시　병점구　영통로　１４－１０　１０５호（반월동，토마토프라자）　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">0391955</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
@@ -1032,42 +1032,42 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">0465865</t>
+          <t xml:space="preserve">0734062</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">우체국　　　　　　　</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">우성　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">홍성우체국　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  744  5551 </t>
+          <t xml:space="preserve">041  632  2014 </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  744  5552 </t>
+          <t xml:space="preserve">041  633  2006 </t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">38076 </t>
+          <t xml:space="preserve">32247 </t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260618</t>
+          <t xml:space="preserve">20260619</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상북도　경주시　유림로　１０７　（용강동，　두산위브트레지움）　근린생활시설２동　２０３호　　　　</t>
+          <t xml:space="preserve">충청남도　홍성군　홍성읍　내포로　１１１　（홍성읍，홍성우체국）　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1079,193 +1079,193 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">0502155</t>
+          <t xml:space="preserve">0746623</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">저축은행　　　　　　</t>
+          <t xml:space="preserve">우체국　　　　　　　</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">유니온　　　기업금융관리팀　　</t>
+          <t xml:space="preserve">광주오치동우체국　　　　　　　</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  256  4000 </t>
+          <t xml:space="preserve">062  264  2704 </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  255  8709 </t>
+          <t xml:space="preserve">062  267  1375 </t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">41951 </t>
+          <t xml:space="preserve">61122 </t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260618</t>
+          <t xml:space="preserve">20260619</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">대구광역시　중구　달구벌대로　２２１０　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">광주광역시　북구　서하로　２４１　（오치동，오치동우체국）　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">0502087</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">0502184</t>
+          <t xml:space="preserve">0748333</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">저축은행　　　　　　</t>
+          <t xml:space="preserve">우체국　　　　　　　</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">유니온　　　오토금융팀　　　　</t>
+          <t xml:space="preserve">금융원２지급센터　　　　　　　</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  256  4000 </t>
+          <t xml:space="preserve">062  375  7430 </t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  256  4006 </t>
+          <t xml:space="preserve">               </t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">41935 </t>
+          <t xml:space="preserve">61947 </t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260618</t>
+          <t xml:space="preserve">20260619</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">대구광역시　중구　국채보상로　５７０　－１，　유니온저축은행　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">광주광역시　서구　상무중앙로　１１０　（치평동，우체국보험광주회관）　４층　청구심사２팀　　　　　　</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t xml:space="preserve">0502087</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">0502197</t>
+          <t xml:space="preserve">4920021</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">저축은행　　　　　　</t>
+          <t xml:space="preserve">중소벤처기업진흥공단</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">유니온　　　기업금융１팀　　　</t>
+          <t xml:space="preserve">본사　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  256  4000 </t>
+          <t xml:space="preserve">055  751  9607 </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  256  4006 </t>
+          <t xml:space="preserve">0505 047  4414 </t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">41935 </t>
+          <t xml:space="preserve">52851 </t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260618</t>
+          <t xml:space="preserve">20260619</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">대구광역시　중구　국채보상로　５７０－１　유니온저축은행　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　진주시　동진로　４３０　（충무공동）　대출관리실　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t xml:space="preserve">0502087</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">잠정패쇄</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">0502207</t>
+          <t xml:space="preserve">0183176</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">저축은행　　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">유니온　　　전략영업１팀　　　</t>
+          <t xml:space="preserve">일산　풍산역　　　　　　　　　</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  256  4000 </t>
+          <t xml:space="preserve">031  977  8062 </t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  255  8709 </t>
+          <t xml:space="preserve">031  977  8063 </t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">41951 </t>
+          <t xml:space="preserve">10355 </t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1275,12 +1275,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">대구광역시　중구　달구벌대로　２２１０　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　고양시　일산동구　중산로　６３　현대프라자　２０１호　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t xml:space="preserve">0502087</t>
+          <t xml:space="preserve">0122409</t>
         </is>
       </c>
     </row>
@@ -1292,32 +1292,32 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">0502210</t>
+          <t xml:space="preserve">0390231</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">저축은행　　　　　　</t>
+          <t xml:space="preserve">경남　　　　　　　　</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">유니온　　　전략영업３팀　　　</t>
+          <t xml:space="preserve">통합제도부　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  256  4000 </t>
+          <t xml:space="preserve">055  290  8381 </t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  423  3009 </t>
+          <t xml:space="preserve">0505 082  6067 </t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">41951 </t>
+          <t xml:space="preserve">51316 </t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1327,49 +1327,49 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">대구광역시　중구　달구벌대로　２２１０　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　창원시　마산회원구　３·１５대로　６４２　（석전동）　６４２　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t xml:space="preserve">0502087</t>
+          <t xml:space="preserve">0390671</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">0509459</t>
+          <t xml:space="preserve">0390532</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">저축은행　　　　　　</t>
+          <t xml:space="preserve">경남　　　　　　　　</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">유니온　　　본부　　　　　　　</t>
+          <t xml:space="preserve">디지털전략부　　　　　　　　　</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  256  4000 </t>
+          <t xml:space="preserve">055  290  8000 </t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  256  4000 </t>
+          <t xml:space="preserve">055  290  8993 </t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">41935 </t>
+          <t xml:space="preserve">630807</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1379,12 +1379,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">대구광역시　중구　국채보상로　５７０－１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　창원시　마산회원구　３·１５대로　６４２　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t xml:space="preserve">0502087</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
@@ -1396,32 +1396,32 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">0874346</t>
+          <t xml:space="preserve">0390862</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">경남　　　　　　　　</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">우성새마을금고황오동지점　　　</t>
+          <t xml:space="preserve">비대면마케팅부　　　　　　　　</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  777  5551 </t>
+          <t xml:space="preserve">055  290  8000 </t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  777  5552 </t>
+          <t xml:space="preserve">055  290  8000 </t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">38159 </t>
+          <t xml:space="preserve">51316 </t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상북도　경주시　원효로　１４６　우성금고황오동지점　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　창원시　마산회원구　３·１５대로　６４２（석전동）　디지털마케팅부　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1443,52 +1443,52 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">0130941</t>
+          <t xml:space="preserve">0391942</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">경남　　　　　　　　</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">태안　망포　　　　　　　　　　</t>
+          <t xml:space="preserve">윤리경영부　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  205  1106 </t>
+          <t xml:space="preserve">055  1588 8585 </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  205  1107 </t>
+          <t xml:space="preserve">0505 082  5300 </t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">16692 </t>
+          <t xml:space="preserve">51316 </t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260617</t>
+          <t xml:space="preserve">20260618</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　수원시　영통구　영통로９０번길　７　（망포동）　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　창원시　마산회원구　３·１５대로　６４２　（석전동）　윤리경영부　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0391955</t>
         </is>
       </c>
     </row>
@@ -1500,42 +1500,42 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">0133689</t>
+          <t xml:space="preserve">0465865</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">경주　내남　　　　　　　　　　</t>
+          <t xml:space="preserve">우성　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  748  2641 </t>
+          <t xml:space="preserve">054  744  5551 </t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  748  3642 </t>
+          <t xml:space="preserve">054  744  5552 </t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">38193 </t>
+          <t xml:space="preserve">38076 </t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260617</t>
+          <t xml:space="preserve">20260618</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상북도　경주시　내남면　이조중앙길　１７　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상북도　경주시　유림로　１０７　（용강동，　두산위브트레지움）　근린생활시설２동　２０３호　　　　</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1547,312 +1547,312 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">0141367</t>
+          <t xml:space="preserve">0502155</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">저축은행　　　　　　</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">태안　기배　　　　　　　　　　</t>
+          <t xml:space="preserve">유니온　　　기업금융관리팀　　</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  267  3245 </t>
+          <t xml:space="preserve">053  256  4000 </t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  267  3249 </t>
+          <t xml:space="preserve">053  255  8709 </t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">18341 </t>
+          <t xml:space="preserve">41951 </t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260617</t>
+          <t xml:space="preserve">20260618</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　화성시　효행구　기안남로　７０　（기안동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">대구광역시　중구　달구벌대로　２２１０　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0502087</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">0155256</t>
+          <t xml:space="preserve">0502184</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">저축은행　　　　　　</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">태안　기산　　　　　　　　　　</t>
+          <t xml:space="preserve">유니온　　　오토금융팀　　　　</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  221  3066 </t>
+          <t xml:space="preserve">053  256  4000 </t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  221  3098 </t>
+          <t xml:space="preserve">053  256  4006 </t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">18385 </t>
+          <t xml:space="preserve">41935 </t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260617</t>
+          <t xml:space="preserve">20260618</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　화성시　병점구　효행로　１１６１　２０３호（기산동，　대림프라자）　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">대구광역시　중구　국채보상로　５７０　－１，　유니온저축은행　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0502087</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">0156077</t>
+          <t xml:space="preserve">0502197</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">저축은행　　　　　　</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">태안　구봉　　　　　　　　　　</t>
+          <t xml:space="preserve">유니온　　　기업금융１팀　　　</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  225  7480 </t>
+          <t xml:space="preserve">053  256  4000 </t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  225  7484 </t>
+          <t xml:space="preserve">053  256  4006 </t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">18409 </t>
+          <t xml:space="preserve">41935 </t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260617</t>
+          <t xml:space="preserve">20260618</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　화성시　병점구　병점２로　６９　（병점동，재성빌딩）　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">대구광역시　중구　국채보상로　５７０－１　유니온저축은행　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0502087</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">0158910</t>
+          <t xml:space="preserve">0502207</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">저축은행　　　　　　</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">태안　태장　　　　　　　　　　</t>
+          <t xml:space="preserve">유니온　　　전략영업１팀　　　</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  202  1801 </t>
+          <t xml:space="preserve">053  256  4000 </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  202  1866 </t>
+          <t xml:space="preserve">053  255  8709 </t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">16685 </t>
+          <t xml:space="preserve">41951 </t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260617</t>
+          <t xml:space="preserve">20260618</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　수원시　영통구　덕영대로　１４７０　１１６호（망포동，　플래티넘베이스）　　　　　　　　　　</t>
+          <t xml:space="preserve">대구광역시　중구　달구벌대로　２２１０　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0502087</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">0182012</t>
+          <t xml:space="preserve">0502210</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">저축은행　　　　　　</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">태안농협　능동　　　　　　　　</t>
+          <t xml:space="preserve">유니온　　　전략영업３팀　　　</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  234  1100 </t>
+          <t xml:space="preserve">053  256  4000 </t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  237  9912 </t>
+          <t xml:space="preserve">053  423  3009 </t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">18421 </t>
+          <t xml:space="preserve">41951 </t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260617</t>
+          <t xml:space="preserve">20260618</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　화성시　병점구　동탄지성로　１６６　（능동）　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">대구광역시　중구　달구벌대로　２２１０　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0502087</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">0185297</t>
+          <t xml:space="preserve">0509459</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">저축은행　　　　　　</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">충북낙농　서현　　　　　　　　</t>
+          <t xml:space="preserve">유니온　　　본부　　　　　　　</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  233  5536 </t>
+          <t xml:space="preserve">053  256  4000 </t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  233  5538 </t>
+          <t xml:space="preserve">053  256  4000 </t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">28382 </t>
+          <t xml:space="preserve">41935 </t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260617</t>
+          <t xml:space="preserve">20260618</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">충청북도　청주시　흥덕구　서현남로　１６　１층　１１１호（가경동　６３９－１）　　　　　　　　　　　</t>
+          <t xml:space="preserve">대구광역시　중구　국채보상로　５７０－１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0502087</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">0861906</t>
+          <t xml:space="preserve">0874346</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1874,32 +1874,32 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">신포항금고제１지점　　　　　　</t>
+          <t xml:space="preserve">우성새마을금고황오동지점　　　</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  281  3766 </t>
+          <t xml:space="preserve">054  777  5551 </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  281  3770 </t>
+          <t xml:space="preserve">054  777  5552 </t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">37690 </t>
+          <t xml:space="preserve">38159 </t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260617</t>
+          <t xml:space="preserve">20260618</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상북도　포항시　북구　이동로　４７　（득량동）　삼구트리니엔시그니처　제　１３１동　１０２호　　　</t>
+          <t xml:space="preserve">경상북도　경주시　원효로　１４６　우성금고황오동지점　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -1916,32 +1916,32 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">0873127</t>
+          <t xml:space="preserve">0130941</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">중부금고지금지점　　　　　　　</t>
+          <t xml:space="preserve">태안　망포　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  577  7771 </t>
+          <t xml:space="preserve">031  205  1106 </t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  521  9888 </t>
+          <t xml:space="preserve">031  205  1107 </t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">12284 </t>
+          <t xml:space="preserve">16692 </t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　남양주시　다산지금로　１４１　２층　중부금고　지금지점　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　수원시　영통구　영통로９０번길　７　（망포동）　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -1963,37 +1963,37 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877712</t>
+          <t xml:space="preserve">0133689</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">평화금고　송림지점　　　　　　</t>
+          <t xml:space="preserve">경주　내남　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">032  764  7081 </t>
+          <t xml:space="preserve">054  748  2641 </t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">032  777  2182 </t>
+          <t xml:space="preserve">054  748  3642 </t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">22570 </t>
+          <t xml:space="preserve">38193 </t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">인천광역시　동구　송림로１６２번길　１０　（송림동，　송림파인앤유）　１층　１１７호，　１１８호　　</t>
+          <t xml:space="preserve">경상북도　경주시　내남면　이조중앙길　１７　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2015,37 +2015,37 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877725</t>
+          <t xml:space="preserve">0141367</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">평화금고　로타리지점　　　　　</t>
+          <t xml:space="preserve">태안　기배　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">032  765  6688 </t>
+          <t xml:space="preserve">031  267  3245 </t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">032  765  6686 </t>
+          <t xml:space="preserve">031  267  3249 </t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">22543 </t>
+          <t xml:space="preserve">18341 </t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">인천광역시　동구　솔빛로９１번길　７　（송림동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　화성시　효행구　기안남로　７０　（기안동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2067,37 +2067,37 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877738</t>
+          <t xml:space="preserve">0155256</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">팔달금고　세화지점　　　　　　</t>
+          <t xml:space="preserve">태안　기산　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  236  9970 </t>
+          <t xml:space="preserve">031  221  3066 </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  236  2106 </t>
+          <t xml:space="preserve">031  221  3098 </t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">16587 </t>
+          <t xml:space="preserve">18385 </t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　수원시　권선구　정조로　５３７　（세류동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　화성시　병점구　효행로　１１６１　２０３호（기산동，　대림프라자）　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2119,37 +2119,37 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877741</t>
+          <t xml:space="preserve">0156077</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">팔달금고　권선지점　　　　　　</t>
+          <t xml:space="preserve">태안　구봉　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  236  9975 </t>
+          <t xml:space="preserve">031  225  7480 </t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  234  7981 </t>
+          <t xml:space="preserve">031  225  7484 </t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">16589 </t>
+          <t xml:space="preserve">18409 </t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　수원시　권선구　세지로２８번길　４２　（세류동）　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　화성시　병점구　병점２로　６９　（병점동，재성빌딩）　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2176,42 +2176,42 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">0701228</t>
+          <t xml:space="preserve">0158910</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">수협중앙회　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">거제수협　외대역금융센터　　　</t>
+          <t xml:space="preserve">태안　태장　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   962  2280 </t>
+          <t xml:space="preserve">031  202  1801 </t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   962  2282 </t>
+          <t xml:space="preserve">031  202  1866 </t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">02418 </t>
+          <t xml:space="preserve">16685 </t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260616</t>
+          <t xml:space="preserve">20260617</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　동대문구　이문로　１２０　（이문동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　수원시　영통구　덕영대로　１４７０　１１６호（망포동，　플래티넘베이스）　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2228,42 +2228,42 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">0802525</t>
+          <t xml:space="preserve">0182012</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나　　　　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">골드클럽　올림픽선수촌ＰＢ센터</t>
+          <t xml:space="preserve">태안농협　능동　　　　　　　　</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   406  6672 </t>
+          <t xml:space="preserve">031  234  1100 </t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   400  4069 </t>
+          <t xml:space="preserve">031  237  9912 </t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">05648 </t>
+          <t xml:space="preserve">18421 </t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260615</t>
+          <t xml:space="preserve">20260617</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울　송파구　양재대로　１２２２　（방이동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　화성시　병점구　동탄지성로　１６６　（능동）　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2280,42 +2280,42 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">0811639</t>
+          <t xml:space="preserve">0185297</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나　　　　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">화곡역금융센터　　　　　　　　</t>
+          <t xml:space="preserve">충북낙농　서현　　　　　　　　</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2693 1111 </t>
+          <t xml:space="preserve">043  233  5536 </t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2607 0830 </t>
+          <t xml:space="preserve">043  233  5538 </t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">157922</t>
+          <t xml:space="preserve">28382 </t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260615</t>
+          <t xml:space="preserve">20260617</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울　강서구　화곡３동　１０５１－１７번지　대사빌딩　１층　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">충청북도　청주시　흥덕구　서현남로　１６　１층　１１１호（가경동　６３９－１）　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2332,42 +2332,42 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">0812366</t>
+          <t xml:space="preserve">0861906</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나　　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">골드클럽　아시아선수촌ＰＢ센터</t>
+          <t xml:space="preserve">신포항금고제１지점　　　　　　</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   472  1111 </t>
+          <t xml:space="preserve">054  281  3766 </t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   420  2322 </t>
+          <t xml:space="preserve">054  281  3770 </t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">138797</t>
+          <t xml:space="preserve">37690 </t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260615</t>
+          <t xml:space="preserve">20260617</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울　송파구　잠실７동　８５－１　아시아선수촌상가１층　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상북도　포항시　북구　이동로　４７　（득량동）　삼구트리니엔시그니처　제　１３１동　１０２호　　　</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2384,42 +2384,42 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">0812816</t>
+          <t xml:space="preserve">0873127</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나　　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">왕십리금융센터　　　　　　　　</t>
+          <t xml:space="preserve">중부금고지금지점　　　　　　　</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2294 1111 </t>
+          <t xml:space="preserve">031  577  7771 </t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2297 7181 </t>
+          <t xml:space="preserve">031  521  9888 </t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">133030</t>
+          <t xml:space="preserve">12284 </t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260615</t>
+          <t xml:space="preserve">20260617</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울시　성동구　홍익동　１２５　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　남양주시　다산지금로　１４１　２층　중부금고　지금지점　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2431,47 +2431,47 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">0819204</t>
+          <t xml:space="preserve">0877712</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나　　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">골드클럽　영업１부　ＰＢ센터　</t>
+          <t xml:space="preserve">평화금고　송림지점　　　　　　</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   737  1111 </t>
+          <t xml:space="preserve">032  764  7081 </t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   757  6692 </t>
+          <t xml:space="preserve">032  777  2182 </t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">04523 </t>
+          <t xml:space="preserve">22570 </t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260615</t>
+          <t xml:space="preserve">20260617</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　중구　을지로　３５（을지로１가）　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">인천광역시　동구　송림로１６２번길　１０　（송림동，　송림파인앤유）　１층　１１７호，　１１８호　　</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877699</t>
+          <t xml:space="preserve">0877725</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">동군산금고　양안금고　　　　　</t>
+          <t xml:space="preserve">평화금고　로타리지점　　　　　</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  471  2442 </t>
+          <t xml:space="preserve">032  765  6688 </t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  451  4777 </t>
+          <t xml:space="preserve">032  765  6686 </t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">54074 </t>
+          <t xml:space="preserve">22543 </t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260615</t>
+          <t xml:space="preserve">20260617</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">전북특별자치도　군산시　부골１길　４７　（조촌동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">인천광역시　동구　솔빛로９１번길　７　（송림동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877709</t>
+          <t xml:space="preserve">0877738</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2550,32 +2550,32 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">동군산금고　발산지점　　　　　</t>
+          <t xml:space="preserve">팔달금고　세화지점　　　　　　</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  451  4334 </t>
+          <t xml:space="preserve">031  236  9970 </t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  451  4774 </t>
+          <t xml:space="preserve">031  236  2106 </t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">54065 </t>
+          <t xml:space="preserve">16587 </t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260615</t>
+          <t xml:space="preserve">20260617</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">전북특별자치도　군산시　개정면　바르메길　３９　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　수원시　권선구　정조로　５３７　（세류동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2587,47 +2587,47 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2708504</t>
+          <t xml:space="preserve">0877741</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나증권　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">전주　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">팔달금고　권선지점　　　　　　</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  276  1212 </t>
+          <t xml:space="preserve">031  236  9975 </t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  253  2033 </t>
+          <t xml:space="preserve">031  234  7981 </t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">54966 </t>
+          <t xml:space="preserve">16589 </t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260615</t>
+          <t xml:space="preserve">20260617</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">전북특별자치도　전주시　완산구　홍산로　２６１　（효자동２가），　ＢＹＣ건물　１층　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　수원시　권선구　세지로２８번길　４２　（세류동）　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -2644,42 +2644,42 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">0459473</t>
+          <t xml:space="preserve">0701228</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">수협중앙회　　　　　</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">나주동부　　　　　　　　　　　</t>
+          <t xml:space="preserve">거제수협　외대역금융센터　　　</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  331  1557 </t>
+          <t xml:space="preserve">02   962  2280 </t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  331  5547 </t>
+          <t xml:space="preserve">02   962  2282 </t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">58227 </t>
+          <t xml:space="preserve">02418 </t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260612</t>
+          <t xml:space="preserve">20260616</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">전라남도　나주시　남평읍　강변１길　７３－１２　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　동대문구　이문로　１２０　（이문동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -2696,42 +2696,42 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">0874786</t>
+          <t xml:space="preserve">0802525</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">하나　　　　　　　　</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">소양강금고약사지점　　　　　　</t>
+          <t xml:space="preserve">골드클럽　올림픽선수촌ＰＢ센터</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">033  252  7559 </t>
+          <t xml:space="preserve">02   406  6672 </t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">033  252  7550 </t>
+          <t xml:space="preserve">02   400  4069 </t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">24357 </t>
+          <t xml:space="preserve">05648 </t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260612</t>
+          <t xml:space="preserve">20260615</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">강원특별자치도　춘천시　공지로　４００　－１００５　１층　１０６호　소양강금고　약사지점　　　　　　</t>
+          <t xml:space="preserve">서울　송파구　양재대로　１２２２　（방이동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -2748,42 +2748,42 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">0875235</t>
+          <t xml:space="preserve">0811639</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">하나　　　　　　　　</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">나주동부금고남평지점　　　　　</t>
+          <t xml:space="preserve">화곡역금융센터　　　　　　　　</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  336  1557 </t>
+          <t xml:space="preserve">02   2693 1111 </t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  336  5547 </t>
+          <t xml:space="preserve">02   2607 0830 </t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">58227 </t>
+          <t xml:space="preserve">157922</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260612</t>
+          <t xml:space="preserve">20260615</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">전라남도　나주시　남평읍　남평２로　４１－５　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울　강서구　화곡３동　１０５１－１７번지　대사빌딩　１층　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -2795,12 +2795,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">0805810</t>
+          <t xml:space="preserve">0812366</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">검단구청　　　　　　　　　　　</t>
+          <t xml:space="preserve">골드클럽　아시아선수촌ＰＢ센터</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">032  766  1111 </t>
+          <t xml:space="preserve">02   472  1111 </t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">032  262  1092 </t>
+          <t xml:space="preserve">02   420  2322 </t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">22679 </t>
+          <t xml:space="preserve">138797</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260611</t>
+          <t xml:space="preserve">20260615</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">인천광역시　서구　독정로１２５번길　１２　（당하동）　당하동　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울　송파구　잠실７동　８５－１　아시아선수촌상가１층　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -2852,42 +2852,42 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">0121015</t>
+          <t xml:space="preserve">0812816</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">하나　　　　　　　　</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">금왕농협　　　　　　　　　　　</t>
+          <t xml:space="preserve">왕십리금융센터　　　　　　　　</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  877  0841 </t>
+          <t xml:space="preserve">02   2294 1111 </t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">0503 8880 2300 </t>
+          <t xml:space="preserve">02   2297 7181 </t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">27629 </t>
+          <t xml:space="preserve">133030</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260610</t>
+          <t xml:space="preserve">20260615</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">충청북도　음성군　금왕읍　무극로　２９３　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울시　성동구　홍익동　１２５　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -2904,42 +2904,42 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">0144005</t>
+          <t xml:space="preserve">0819204</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">하나　　　　　　　　</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">동부　낙서　　　　　　　　　　</t>
+          <t xml:space="preserve">골드클럽　영업１부　ＰＢ센터　</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  572  7018 </t>
+          <t xml:space="preserve">02   737  1111 </t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">0503 8880 5630 </t>
+          <t xml:space="preserve">02   757  6692 </t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">52108 </t>
+          <t xml:space="preserve">04523 </t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260610</t>
+          <t xml:space="preserve">20260615</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　의령군　낙서면　낙서로　５２３　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　중구　을지로　３５（을지로１가）　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -2951,47 +2951,47 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">0150691</t>
+          <t xml:space="preserve">0877699</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">탕정　동산　　　　　　　　　　</t>
+          <t xml:space="preserve">동군산금고　양안금고　　　　　</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">041  534  1811 </t>
+          <t xml:space="preserve">063  471  2442 </t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">041  534  1904 </t>
+          <t xml:space="preserve">063  451  4777 </t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">31458 </t>
+          <t xml:space="preserve">54074 </t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260610</t>
+          <t xml:space="preserve">20260615</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">충청남도　아산시　탕정면　삼성로　４４０　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전북특별자치도　군산시　부골１길　４７　（조촌동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3003,12 +3003,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">0850739</t>
+          <t xml:space="preserve">0877709</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3018,32 +3018,32 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">광양시금고마동지점　　　　　　</t>
+          <t xml:space="preserve">동군산금고　발산지점　　　　　</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  797  1490 </t>
+          <t xml:space="preserve">063  451  4334 </t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  795  8776 </t>
+          <t xml:space="preserve">063  451  4774 </t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">57778 </t>
+          <t xml:space="preserve">54065 </t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260610</t>
+          <t xml:space="preserve">20260615</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남　광양시　진등길　５５－５　송보５차상가내　５１０－２０２　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전북특별자치도　군산시　개정면　바르메길　３９　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3060,42 +3060,42 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">0043562</t>
+          <t xml:space="preserve">2708504</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＫＢ국민　　　　　　</t>
+          <t xml:space="preserve">하나증권　　　　　　</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">휘경동　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전주　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2215 0963 </t>
+          <t xml:space="preserve">063  276  1212 </t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2215 5040 </t>
+          <t xml:space="preserve">063  253  2033 </t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">02418 </t>
+          <t xml:space="preserve">54966 </t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260608</t>
+          <t xml:space="preserve">20260615</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　동대문구　이문로　１２０　（이문동），４１２－１번지　２층　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전북특별자치도　전주시　완산구　홍산로　２６１　（효자동２가），　ＢＹＣ건물　１층　　　　　　　　　</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3112,42 +3112,42 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">0105109</t>
+          <t xml:space="preserve">0459473</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">북의왕　　　　　　　　　　　　</t>
+          <t xml:space="preserve">나주동부　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  425  0432 </t>
+          <t xml:space="preserve">061  331  1557 </t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  425  0430 </t>
+          <t xml:space="preserve">061  331  5547 </t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">16024 </t>
+          <t xml:space="preserve">58227 </t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260608</t>
+          <t xml:space="preserve">20260612</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　의왕시　포일로　２０　（내손동）　래미안에버하임아파트　１층　상가　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전라남도　나주시　남평읍　강변１길　７３－１２　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3164,42 +3164,42 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">0153818</t>
+          <t xml:space="preserve">0874786</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">태안　영통동　　　　　　　　　</t>
+          <t xml:space="preserve">소양강금고약사지점　　　　　　</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  204  3891 </t>
+          <t xml:space="preserve">033  252  7559 </t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  204  3895 </t>
+          <t xml:space="preserve">033  252  7550 </t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">16701 </t>
+          <t xml:space="preserve">24357 </t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260608</t>
+          <t xml:space="preserve">20260612</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　수원시　영통구　매영로　３６８　（영통동，　살구골현대아파트상가）　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">강원특별자치도　춘천시　공지로　４００　－１００５　１층　１０６호　소양강금고　약사지점　　　　　　</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3216,42 +3216,42 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">0804031</t>
+          <t xml:space="preserve">0875235</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나　　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">골드클럽　강남파이낸스ＰＢ센터</t>
+          <t xml:space="preserve">나주동부금고남평지점　　　　　</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   554  3076 </t>
+          <t xml:space="preserve">061  336  1557 </t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   562  5509 </t>
+          <t xml:space="preserve">061  336  5547 </t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">06236 </t>
+          <t xml:space="preserve">58227 </t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260608</t>
+          <t xml:space="preserve">20260612</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울　강남구　테헤란로　１５２　（역삼동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전라남도　나주시　남평읍　남평２로　４１－５　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3263,12 +3263,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">0805690</t>
+          <t xml:space="preserve">0805810</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3278,32 +3278,32 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">골드클럽　여의도ＰＢ센터　　　</t>
+          <t xml:space="preserve">검단구청　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   765  1111 </t>
+          <t xml:space="preserve">032  766  1111 </t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   784  8128 </t>
+          <t xml:space="preserve">032  262  1092 </t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">07339 </t>
+          <t xml:space="preserve">22679 </t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260608</t>
+          <t xml:space="preserve">20260611</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　브라이튼여의도　２층　　　</t>
+          <t xml:space="preserve">인천광역시　서구　독정로１２５번길　１２　（당하동）　당하동　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3320,42 +3320,42 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">0811451</t>
+          <t xml:space="preserve">0121015</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나　　　　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">골드클럽　평창동ＰＢ센터　　　</t>
+          <t xml:space="preserve">금왕농협　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   391  1111 </t>
+          <t xml:space="preserve">043  877  0841 </t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   395  8047 </t>
+          <t xml:space="preserve">0503 8880 2300 </t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">03009 </t>
+          <t xml:space="preserve">27629 </t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260608</t>
+          <t xml:space="preserve">20260610</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　종로구　평창문화로　８７　창진파크팰리스　１층　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">충청북도　음성군　금왕읍　무극로　２９３　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3372,42 +3372,42 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">0814173</t>
+          <t xml:space="preserve">0144005</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나　　　　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">골드클럽　분당ＰＢ센터　　　　</t>
+          <t xml:space="preserve">동부　낙서　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  779  1111 </t>
+          <t xml:space="preserve">055  572  7018 </t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  779  1222 </t>
+          <t xml:space="preserve">0503 8880 5630 </t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">463050</t>
+          <t xml:space="preserve">52108 </t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260608</t>
+          <t xml:space="preserve">20260610</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　성남시　분당구　서현동　２６５－２번지　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　의령군　낙서면　낙서로　５２３　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3424,42 +3424,42 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">0815732</t>
+          <t xml:space="preserve">0150691</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나　　　　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">골드클럽　용산ＰＢ센터　　　　</t>
+          <t xml:space="preserve">탕정　동산　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   797  1111 </t>
+          <t xml:space="preserve">041  534  1811 </t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   797  8795 </t>
+          <t xml:space="preserve">041  534  1904 </t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">140240</t>
+          <t xml:space="preserve">31458 </t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260608</t>
+          <t xml:space="preserve">20260610</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울시　용산구　서빙고동　２７１－１０６외　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">충청남도　아산시　탕정면　삼성로　４４０　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3476,42 +3476,42 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">0819178</t>
+          <t xml:space="preserve">0850739</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나　　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">골드클럽　압구정ＰＢ센터　　　</t>
+          <t xml:space="preserve">광양시금고마동지점　　　　　　</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   512  1111 </t>
+          <t xml:space="preserve">061  797  1490 </t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   542  9872 </t>
+          <t xml:space="preserve">061  795  8776 </t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">135894</t>
+          <t xml:space="preserve">57778 </t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260608</t>
+          <t xml:space="preserve">20260610</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울　강남구　신사동　６１８－３　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전남　광양시　진등길　５５－５　송보５차상가내　５１０－２０２　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -3523,37 +3523,37 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877660</t>
+          <t xml:space="preserve">0043562</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">ＫＢ국민　　　　　　</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">이천금고　장호원지점　　　　　</t>
+          <t xml:space="preserve">휘경동　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  641  3140 </t>
+          <t xml:space="preserve">02   2215 0963 </t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  642  3141 </t>
+          <t xml:space="preserve">02   2215 5040 </t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">17418 </t>
+          <t xml:space="preserve">02418 </t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　이천시　장호원읍　장감로　８１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　동대문구　이문로　１２０　（이문동），４１２－１번지　２층　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -3575,37 +3575,37 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877673</t>
+          <t xml:space="preserve">0105109</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">이천금고　신하지점　　　　　　</t>
+          <t xml:space="preserve">북의왕　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  634  3774 </t>
+          <t xml:space="preserve">031  425  0432 </t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  634  3776 </t>
+          <t xml:space="preserve">031  425  0430 </t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">17327 </t>
+          <t xml:space="preserve">16024 </t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　이천시　부발읍　경충대로　２２３６　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　의왕시　포일로　２０　（내손동）　래미안에버하임아파트　１층　상가　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -3627,37 +3627,37 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877686</t>
+          <t xml:space="preserve">0153818</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">이천금고　마장지점　　　　　　</t>
+          <t xml:space="preserve">태안　영통동　　　　　　　　　</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  633  3140 </t>
+          <t xml:space="preserve">031  204  3891 </t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  631  3141 </t>
+          <t xml:space="preserve">031  204  3895 </t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">17387 </t>
+          <t xml:space="preserve">16701 </t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　이천시　마장면　오천로　５１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　수원시　영통구　매영로　３６８　（영통동，　살구골현대아파트상가）　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -3684,42 +3684,42 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">0233000</t>
+          <t xml:space="preserve">0804031</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＳＣ제일　　　　　　</t>
+          <t xml:space="preserve">하나　　　　　　　　</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">홍대입구역　　　　　　　　　　</t>
+          <t xml:space="preserve">골드클럽　강남파이낸스ＰＢ센터</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   334  0123 </t>
+          <t xml:space="preserve">02   554  3076 </t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   334  0047 </t>
+          <t xml:space="preserve">02   562  5509 </t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">04056 </t>
+          <t xml:space="preserve">06236 </t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260605</t>
+          <t xml:space="preserve">20260608</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　마포구　신촌로　１２　２층　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울　강남구　테헤란로　１５２　（역삼동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -3736,42 +3736,42 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">0234805</t>
+          <t xml:space="preserve">0805690</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＳＣ제일　　　　　　</t>
+          <t xml:space="preserve">하나　　　　　　　　</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">송도국제도시　　　　　　　　　</t>
+          <t xml:space="preserve">골드클럽　여의도ＰＢ센터　　　</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">032  834  3535 </t>
+          <t xml:space="preserve">02   765  1111 </t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">032  834  3883 </t>
+          <t xml:space="preserve">02   784  8128 </t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">406840</t>
+          <t xml:space="preserve">07339 </t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260605</t>
+          <t xml:space="preserve">20260608</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">인천　연수구　송도동　３－２５　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　브라이튼여의도　２층　　　</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -3783,47 +3783,47 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877657</t>
+          <t xml:space="preserve">0811451</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">하나　　　　　　　　</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">금강금고　사비지점　　　　　　</t>
+          <t xml:space="preserve">골드클럽　평창동ＰＢ센터　　　</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">041  408  8282 </t>
+          <t xml:space="preserve">02   391  1111 </t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">041  408  8283 </t>
+          <t xml:space="preserve">02   395  8047 </t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">33158 </t>
+          <t xml:space="preserve">03009 </t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260605</t>
+          <t xml:space="preserve">20260608</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">충청남도　부여군　부여읍　성왕로　３５０－１　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　종로구　평창문화로　８７　창진파크팰리스　１층　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -3840,42 +3840,42 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">0133414</t>
+          <t xml:space="preserve">0814173</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">하나　　　　　　　　</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">입면농협　　　　　　　　　　　</t>
+          <t xml:space="preserve">골드클럽　분당ＰＢ센터　　　　</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  362  6005 </t>
+          <t xml:space="preserve">031  779  1111 </t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">0503 8880 3927 </t>
+          <t xml:space="preserve">031  779  1222 </t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">57513 </t>
+          <t xml:space="preserve">463050</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260604</t>
+          <t xml:space="preserve">20260608</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">전라남도　곡성군　입면　입면로　６８３　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　성남시　분당구　서현동　２６５－２번지　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -3892,42 +3892,42 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">0143640</t>
+          <t xml:space="preserve">0815732</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">하나　　　　　　　　</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">제천　역전　　　　　　　　　　</t>
+          <t xml:space="preserve">골드클럽　용산ＰＢ센터　　　　</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  643  3769 </t>
+          <t xml:space="preserve">02   797  1111 </t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  646  3769 </t>
+          <t xml:space="preserve">02   797  8795 </t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">27196 </t>
+          <t xml:space="preserve">140240</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260604</t>
+          <t xml:space="preserve">20260608</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">충청북도　제천시　내토로　４４２　（화산동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울시　용산구　서빙고동　２７１－１０６외　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -3944,42 +3944,42 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">0452056</t>
+          <t xml:space="preserve">0819178</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">하나　　　　　　　　</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">마포역　　　　　　　　　　　　</t>
+          <t xml:space="preserve">골드클럽　압구정ＰＢ센터　　　</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   713  0324 </t>
+          <t xml:space="preserve">02   512  1111 </t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   703  7846 </t>
+          <t xml:space="preserve">02   542  9872 </t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">04172 </t>
+          <t xml:space="preserve">135894</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260604</t>
+          <t xml:space="preserve">20260608</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　마포구　도화길　１４　（도화동）　２층　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울　강남구　신사동　６１８－３　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -3991,12 +3991,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">0453505</t>
+          <t xml:space="preserve">0877660</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4006,32 +4006,32 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">신신　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">이천금고　장호원지점　　　　　</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   869  2173 </t>
+          <t xml:space="preserve">031  641  3140 </t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   869  2175 </t>
+          <t xml:space="preserve">031  642  3141 </t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">08774 </t>
+          <t xml:space="preserve">17418 </t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260604</t>
+          <t xml:space="preserve">20260608</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　관악구　신원로　１５　（신림동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　이천시　장호원읍　장감로　８１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -4043,12 +4043,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">0866040</t>
+          <t xml:space="preserve">0877673</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4058,32 +4058,32 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">수성１가금고제１지점　　　　　</t>
+          <t xml:space="preserve">이천금고　신하지점　　　　　　</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  763  0165 </t>
+          <t xml:space="preserve">031  634  3774 </t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  756  9717 </t>
+          <t xml:space="preserve">031  634  3776 </t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">42130 </t>
+          <t xml:space="preserve">17327 </t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260604</t>
+          <t xml:space="preserve">20260608</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">대구광역시　수성구　명덕로７６길　６４　（수성동１가）　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　이천시　부발읍　경충대로　２２３６　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -4095,47 +4095,47 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2090830</t>
+          <t xml:space="preserve">0877686</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">유안타증권　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">매직국민　　　　　　　　　　　</t>
+          <t xml:space="preserve">이천금고　마장지점　　　　　　</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3770 2000 </t>
+          <t xml:space="preserve">031  633  3140 </t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   335  7332 </t>
+          <t xml:space="preserve">031  631  3141 </t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">07339 </t>
+          <t xml:space="preserve">17387 </t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260604</t>
+          <t xml:space="preserve">20260608</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　이천시　마장면　오천로　５１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4152,42 +4152,42 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2090869</t>
+          <t xml:space="preserve">0233000</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">유안타증권　　　　　</t>
+          <t xml:space="preserve">ＳＣ제일　　　　　　</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">매직씨티　　　　　　　　　　　</t>
+          <t xml:space="preserve">홍대입구역　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3770 2000 </t>
+          <t xml:space="preserve">02   334  0123 </t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   335  7332 </t>
+          <t xml:space="preserve">02   334  0047 </t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">07339 </t>
+          <t xml:space="preserve">04056 </t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260604</t>
+          <t xml:space="preserve">20260605</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　마포구　신촌로　１２　２층　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4204,42 +4204,42 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2090885</t>
+          <t xml:space="preserve">0234805</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">유안타증권　　　　　</t>
+          <t xml:space="preserve">ＳＣ제일　　　　　　</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">매직우리　　　　　　　　　　　</t>
+          <t xml:space="preserve">송도국제도시　　　　　　　　　</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3770 2000 </t>
+          <t xml:space="preserve">032  834  3535 </t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   335  7332 </t>
+          <t xml:space="preserve">032  834  3883 </t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">07339 </t>
+          <t xml:space="preserve">406840</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260604</t>
+          <t xml:space="preserve">20260605</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">인천　연수구　송도동　３－２５　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4251,47 +4251,47 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2090908</t>
+          <t xml:space="preserve">0877657</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">유안타증권　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">매직신한　　　　　　　　　　　</t>
+          <t xml:space="preserve">금강금고　사비지점　　　　　　</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3770 2000 </t>
+          <t xml:space="preserve">041  408  8282 </t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   335  7332 </t>
+          <t xml:space="preserve">041  408  8283 </t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">07339 </t>
+          <t xml:space="preserve">33158 </t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260604</t>
+          <t xml:space="preserve">20260605</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">충청남도　부여군　부여읍　성왕로　３５０－１　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -4308,32 +4308,32 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2090940</t>
+          <t xml:space="preserve">0133414</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">유안타증권　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">매직기업　　　　　　　　　　　</t>
+          <t xml:space="preserve">입면농협　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3770 2000 </t>
+          <t xml:space="preserve">061  362  6005 </t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   335  7332 </t>
+          <t xml:space="preserve">0503 8880 3927 </t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">07339 </t>
+          <t xml:space="preserve">57513 </t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전라남도　곡성군　입면　입면로　６８３　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -4360,32 +4360,32 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2090953</t>
+          <t xml:space="preserve">0143640</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">유안타증권　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">매직농협　　　　　　　　　　　</t>
+          <t xml:space="preserve">제천　역전　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3770 2000 </t>
+          <t xml:space="preserve">043  643  3769 </t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   335  7332 </t>
+          <t xml:space="preserve">043  646  3769 </t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">07339 </t>
+          <t xml:space="preserve">27196 </t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">충청북도　제천시　내토로　４４２　（화산동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -4412,32 +4412,32 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091046</t>
+          <t xml:space="preserve">0452056</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">유안타증권　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">매직하나　　　　　　　　　　　</t>
+          <t xml:space="preserve">마포역　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3770 2000 </t>
+          <t xml:space="preserve">02   713  0324 </t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   335  7332 </t>
+          <t xml:space="preserve">02   703  7846 </t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">07339 </t>
+          <t xml:space="preserve">04172 </t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　마포구　도화길　１４　（도화동）　２층　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -4464,32 +4464,32 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091211</t>
+          <t xml:space="preserve">0453505</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">유안타증권　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">매직부산　　　　　　　　　　　</t>
+          <t xml:space="preserve">신신　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3770 2000 </t>
+          <t xml:space="preserve">02   869  2173 </t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   335  7332 </t>
+          <t xml:space="preserve">02   869  2175 </t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">07339 </t>
+          <t xml:space="preserve">08774 </t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　관악구　신원로　１５　（신림동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -4516,32 +4516,32 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2092579</t>
+          <t xml:space="preserve">0866040</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">유안타증권　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">매직생명　　　　　　　　　　　</t>
+          <t xml:space="preserve">수성１가금고제１지점　　　　　</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3770 2000 </t>
+          <t xml:space="preserve">053  763  0165 </t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   335  7332 </t>
+          <t xml:space="preserve">053  756  9717 </t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">07339 </t>
+          <t xml:space="preserve">42130 </t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">대구광역시　수성구　명덕로７６길　６４　（수성동１가）　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2092595</t>
+          <t xml:space="preserve">2090830</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">제휴사업팀　ＡＴＭ　　　　　　</t>
+          <t xml:space="preserve">매직국민　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3770 2599 </t>
+          <t xml:space="preserve">02   335  7332 </t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2092650</t>
+          <t xml:space="preserve">2090869</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">고객지원팀　ＶＡＮ　　　　　　</t>
+          <t xml:space="preserve">매직씨티　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3770 2599 </t>
+          <t xml:space="preserve">02   335  7332 </t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2092731</t>
+          <t xml:space="preserve">2090885</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">매직새마을금고　　　　　　　　</t>
+          <t xml:space="preserve">매직우리　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   1588 2600 </t>
+          <t xml:space="preserve">02   3770 2000 </t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2092757</t>
+          <t xml:space="preserve">2090908</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4734,12 +4734,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">매직ＳＣ　　　　　　　　　　　</t>
+          <t xml:space="preserve">매직신한　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   1588 2600 </t>
+          <t xml:space="preserve">02   3770 2000 </t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2092809</t>
+          <t xml:space="preserve">2090940</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4786,17 +4786,17 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ｏｐｅｒａｔｉｏｎ센터점　　　</t>
+          <t xml:space="preserve">매직기업　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3770 5520 </t>
+          <t xml:space="preserve">02   3770 2000 </t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3770 5611 </t>
+          <t xml:space="preserve">02   335  7332 </t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）３２층　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2092812</t>
+          <t xml:space="preserve">2090953</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4838,17 +4838,17 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">스마트센터　　　　　　　　　　</t>
+          <t xml:space="preserve">매직농협　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2012 8000 </t>
+          <t xml:space="preserve">02   3770 2000 </t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3770 2548 </t>
+          <t xml:space="preserve">02   335  7332 </t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2092825</t>
+          <t xml:space="preserve">2091046</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4890,17 +4890,17 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">매직우체국금융　　　　　　　　</t>
+          <t xml:space="preserve">매직하나　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   1588 2600 </t>
+          <t xml:space="preserve">02   3770 2000 </t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2634 7866 </t>
+          <t xml:space="preserve">02   335  7332 </t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -4932,7 +4932,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2092838</t>
+          <t xml:space="preserve">2091211</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4942,17 +4942,17 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">매직경남　　　　　　　　　　　</t>
+          <t xml:space="preserve">매직부산　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   1588 2600 </t>
+          <t xml:space="preserve">02   3770 2000 </t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3770 2548 </t>
+          <t xml:space="preserve">02   335  7332 </t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2095039</t>
+          <t xml:space="preserve">2092579</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">매직동양　　　　　　　　　　　</t>
+          <t xml:space="preserve">매직생명　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5004,7 +5004,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3770 2000 </t>
+          <t xml:space="preserve">02   335  7332 </t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2096009</t>
+          <t xml:space="preserve">2092595</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">신탁운용지점　　　　　　　　　</t>
+          <t xml:space="preserve">제휴사업팀　ＡＴＭ　　　　　　</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3770 7332 </t>
+          <t xml:space="preserve">02   3770 2599 </t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　유안타증권　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2099543</t>
+          <t xml:space="preserve">2092650</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -5098,17 +5098,17 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">고객지원팀　　　　　　　　　　</t>
+          <t xml:space="preserve">고객지원팀　ＶＡＮ　　　　　　</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3770 5605 </t>
+          <t xml:space="preserve">02   3770 2000 </t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3770 2566 </t>
+          <t xml:space="preserve">02   3770 2599 </t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -5140,42 +5140,42 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t xml:space="preserve">0143640</t>
+          <t xml:space="preserve">2092731</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">유안타증권　　　　　</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">제천　역전　　　　　　　　　　</t>
+          <t xml:space="preserve">매직새마을금고　　　　　　　　</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  643  3769 </t>
+          <t xml:space="preserve">02   1588 2600 </t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  646  3769 </t>
+          <t xml:space="preserve">02   335  7332 </t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">27185 </t>
+          <t xml:space="preserve">07339 </t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260602</t>
+          <t xml:space="preserve">20260604</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">충청북도　제천시　내토로　４２１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -5192,42 +5192,42 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">0020242</t>
+          <t xml:space="preserve">2092757</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">산업　　　　　　　　</t>
+          <t xml:space="preserve">유안타증권　　　　　</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">국민성장펀드　첨단산업전략기금</t>
+          <t xml:space="preserve">매직ＳＣ　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   787  4000 </t>
+          <t xml:space="preserve">02   1588 2600 </t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   787  5091 </t>
+          <t xml:space="preserve">02   335  7332 </t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">07242 </t>
+          <t xml:space="preserve">07339 </t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260601</t>
+          <t xml:space="preserve">20260604</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　영등포구　은행로　１４　（여의도동）　한국산업은행　본점　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -5244,42 +5244,42 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">0039521</t>
+          <t xml:space="preserve">2092809</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">기업　　　　　　　　</t>
+          <t xml:space="preserve">유안타증권　　　　　</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">반월기업금융센터　　　　　　　</t>
+          <t xml:space="preserve">Ｏｐｅｒａｔｉｏｎ센터점　　　</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  412  0740 </t>
+          <t xml:space="preserve">02   3770 5520 </t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 075  0952 </t>
+          <t xml:space="preserve">02   3770 5611 </t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">15433 </t>
+          <t xml:space="preserve">07339 </t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260601</t>
+          <t xml:space="preserve">20260604</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　안산시　단원구　동산로　６３　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）３２층　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -5296,42 +5296,42 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t xml:space="preserve">0135810</t>
+          <t xml:space="preserve">2092812</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">유안타증권　　　　　</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">서포농협　　　　　　　　　　　</t>
+          <t xml:space="preserve">스마트센터　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  853  1500 </t>
+          <t xml:space="preserve">02   2012 8000 </t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  853  1506 </t>
+          <t xml:space="preserve">02   3770 2548 </t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">52543 </t>
+          <t xml:space="preserve">07339 </t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260601</t>
+          <t xml:space="preserve">20260604</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　사천시　서포면　사천대교로　７２１　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -5348,42 +5348,42 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t xml:space="preserve">0198983</t>
+          <t xml:space="preserve">2092825</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＫＢ국민　　　　　　</t>
+          <t xml:space="preserve">유안타증권　　　　　</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">전북혁신도시（점）　　　　　　</t>
+          <t xml:space="preserve">매직우체국금융　　　　　　　　</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">000  0000 0000 </t>
+          <t xml:space="preserve">02   1588 2600 </t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">000  0000 0000 </t>
+          <t xml:space="preserve">02   2634 7866 </t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">54871 </t>
+          <t xml:space="preserve">07339 </t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260601</t>
+          <t xml:space="preserve">20260604</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">전북특별자치도　전주시　덕진구　안전로　１４４　（중동）　１층　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -5395,52 +5395,52 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t xml:space="preserve">0507370</t>
+          <t xml:space="preserve">2092838</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">저축은행　　　　　　</t>
+          <t xml:space="preserve">유안타증권　　　　　</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">제이티친애　잠실（지）　　　　</t>
+          <t xml:space="preserve">매직경남　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2240 6300 </t>
+          <t xml:space="preserve">02   1588 2600 </t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   416  0094 </t>
+          <t xml:space="preserve">02   3770 2548 </t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">05502 </t>
+          <t xml:space="preserve">07339 </t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260601</t>
+          <t xml:space="preserve">20260604</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　송파구　올림픽로　１４５，　리센츠상가　４층　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t xml:space="preserve">0507312</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
@@ -5452,42 +5452,42 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t xml:space="preserve">0802130</t>
+          <t xml:space="preserve">2095039</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나　　　　　　　　</t>
+          <t xml:space="preserve">유안타증권　　　　　</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">구로기업센터　　　　　　　　　</t>
+          <t xml:space="preserve">매직동양　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   864  5554 </t>
+          <t xml:space="preserve">02   3770 2000 </t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   868  3390 </t>
+          <t xml:space="preserve">02   3770 2000 </t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">08316 </t>
+          <t xml:space="preserve">07339 </t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260601</t>
+          <t xml:space="preserve">20260604</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　구로구　구로동로　１１５　（구로동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -5504,42 +5504,42 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t xml:space="preserve">0802813</t>
+          <t xml:space="preserve">2096009</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나　　　　　　　　</t>
+          <t xml:space="preserve">유안타증권　　　　　</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">양재금융센터　　　　　　　　　</t>
+          <t xml:space="preserve">신탁운용지점　　　　　　　　　</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   571  6149 </t>
+          <t xml:space="preserve">02   3770 2000 </t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   578  3467 </t>
+          <t xml:space="preserve">02   3770 7332 </t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">06752 </t>
+          <t xml:space="preserve">07339 </t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260601</t>
+          <t xml:space="preserve">20260604</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울　서초구　강남대로２７길　７－１５　（양재동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　유안타증권　　　　　　　　</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -5556,42 +5556,42 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t xml:space="preserve">0804154</t>
+          <t xml:space="preserve">2099543</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나　　　　　　　　</t>
+          <t xml:space="preserve">유안타증권　　　　　</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">공덕동금융센터　　　　　　　　</t>
+          <t xml:space="preserve">고객지원팀　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   715  1372 </t>
+          <t xml:space="preserve">02   3770 5605 </t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   715  1528 </t>
+          <t xml:space="preserve">02   3770 2566 </t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">04143 </t>
+          <t xml:space="preserve">07339 </t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260601</t>
+          <t xml:space="preserve">20260604</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울　마포구　마포대로　１３７　（공덕동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -5608,42 +5608,42 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t xml:space="preserve">0812612</t>
+          <t xml:space="preserve">0143640</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나　　　　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">공덕역금융센터　　　　　　　　</t>
+          <t xml:space="preserve">제천　역전　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   706  1111 </t>
+          <t xml:space="preserve">043  643  3769 </t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   706  4981 </t>
+          <t xml:space="preserve">043  646  3769 </t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">121710</t>
+          <t xml:space="preserve">27185 </t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260601</t>
+          <t xml:space="preserve">20260602</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울　마포구　공덕동　２５４－８　별정우체국연합빌딩　１층　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">충청북도　제천시　내토로　４２１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -5660,32 +5660,32 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t xml:space="preserve">0863726</t>
+          <t xml:space="preserve">0020242</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">산업　　　　　　　　</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">김해시민금고진영１지점　　　　</t>
+          <t xml:space="preserve">국민성장펀드　첨단산업전략기금</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  343  9700 </t>
+          <t xml:space="preserve">02   787  4000 </t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  343  9705 </t>
+          <t xml:space="preserve">02   787  5091 </t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">50865 </t>
+          <t xml:space="preserve">07242 </t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　김해시　진영읍　여래로　２２　김해시민새마을금고　진영지점　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　영등포구　은행로　１４　（여의도동）　한국산업은행　본점　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -5712,32 +5712,32 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2180892</t>
+          <t xml:space="preserve">0039521</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＫＢ증권　　　　　　</t>
+          <t xml:space="preserve">기업　　　　　　　　</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">전북혁신도시라운지　　　　　　</t>
+          <t xml:space="preserve">반월기업금융센터　　　　　　　</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  916  7400 </t>
+          <t xml:space="preserve">031  412  0740 </t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  916  7499 </t>
+          <t xml:space="preserve">0505 075  0952 </t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">54871 </t>
+          <t xml:space="preserve">15433 </t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5747,7 +5747,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">전북특별자치도　전주시　덕진구　안전로　１４４　，　１층　（중동，엔씨빌딩）　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　안산시　단원구　동산로　６３　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -5764,32 +5764,32 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2701103</t>
+          <t xml:space="preserve">0135810</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나증권　　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＴＨＥ　Ｈ１　Ｗ　　　　　　　</t>
+          <t xml:space="preserve">서포농협　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2694 5282 </t>
+          <t xml:space="preserve">055  853  1500 </t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2694 5715 </t>
+          <t xml:space="preserve">055  853  1506 </t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">07998 </t>
+          <t xml:space="preserve">52543 </t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -5799,7 +5799,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　양천구　목동동로　２５７　（목동，　현대하이페리온），　６층　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　사천시　서포면　사천대교로　７２１　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -5811,47 +5811,47 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t xml:space="preserve">0185307</t>
+          <t xml:space="preserve">0198983</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">ＫＢ국민　　　　　　</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">　광혜원　화랑　　　　　　　　</t>
+          <t xml:space="preserve">전북혁신도시（점）　　　　　　</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  000  0000 </t>
+          <t xml:space="preserve">000  0000 0000 </t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  000  0000 </t>
+          <t xml:space="preserve">000  0000 0000 </t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">27805 </t>
+          <t xml:space="preserve">54871 </t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260529</t>
+          <t xml:space="preserve">20260601</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">충청북도　진천군　광혜원면　장기길　９１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전북특별자치도　전주시　덕진구　안전로　１４４　（중동）　１층　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -5863,52 +5863,52 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t xml:space="preserve">0454601</t>
+          <t xml:space="preserve">0507370</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">저축은행　　　　　　</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">부산동구　　　　　　　　　　　</t>
+          <t xml:space="preserve">제이티친애　잠실（지）　　　　</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">051  633  5743 </t>
+          <t xml:space="preserve">02   2240 6300 </t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">051  633  5752 </t>
+          <t xml:space="preserve">02   416  0094 </t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">48735 </t>
+          <t xml:space="preserve">05502 </t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260528</t>
+          <t xml:space="preserve">20260601</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">부산광역시　동구　범일로　１０１－８　（범일동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　송파구　올림픽로　１４５，　리센츠상가　４층　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0507312</t>
         </is>
       </c>
     </row>
@@ -5920,42 +5920,42 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t xml:space="preserve">0874016</t>
+          <t xml:space="preserve">0802130</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">하나　　　　　　　　</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">애플금고　칠금지점　　　　　　</t>
+          <t xml:space="preserve">구로기업센터　　　　　　　　　</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  845  4501 </t>
+          <t xml:space="preserve">02   864  5554 </t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  845  4503 </t>
+          <t xml:space="preserve">02   868  3390 </t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">27354 </t>
+          <t xml:space="preserve">08316 </t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260528</t>
+          <t xml:space="preserve">20260601</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">충청북도　충주시　번영대로　１６　（칠금동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　구로구　구로동로　１１５　（구로동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -5972,42 +5972,42 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t xml:space="preserve">0143064</t>
+          <t xml:space="preserve">0802813</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">하나　　　　　　　　</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">송산　사강　　　　　　　　　　</t>
+          <t xml:space="preserve">양재금융센터　　　　　　　　　</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  357  6800 </t>
+          <t xml:space="preserve">02   571  6149 </t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  357  6880 </t>
+          <t xml:space="preserve">02   578  3467 </t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">18550 </t>
+          <t xml:space="preserve">06752 </t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260527</t>
+          <t xml:space="preserve">20260601</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　화성시　만세구　송산면　사강로　１８８　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울　서초구　강남대로２７길　７－１５　（양재동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -6024,42 +6024,42 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t xml:space="preserve">0143077</t>
+          <t xml:space="preserve">0804154</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">하나　　　　　　　　</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">태안　안녕　　　　　　　　　　</t>
+          <t xml:space="preserve">공덕동금융센터　　　　　　　　</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  236  3301 </t>
+          <t xml:space="preserve">02   715  1372 </t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  236  3002 </t>
+          <t xml:space="preserve">02   715  1528 </t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">18362 </t>
+          <t xml:space="preserve">04143 </t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260527</t>
+          <t xml:space="preserve">20260601</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　화성시　병점구　용주로　２２　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울　마포구　마포대로　１３７　（공덕동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -6076,42 +6076,42 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t xml:space="preserve">0146281</t>
+          <t xml:space="preserve">0812612</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">하나　　　　　　　　</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">한국화훼농협　　　　　　　　　</t>
+          <t xml:space="preserve">공덕역금융센터　　　　　　　　</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  910  8001 </t>
+          <t xml:space="preserve">02   706  1111 </t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  910  8010 </t>
+          <t xml:space="preserve">02   706  4981 </t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">10226 </t>
+          <t xml:space="preserve">121710</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260527</t>
+          <t xml:space="preserve">20260601</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　고양시　일산서구　대화로　３６２　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울　마포구　공덕동　２５４－８　별정우체국연합빌딩　１층　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -6128,42 +6128,42 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t xml:space="preserve">0155227</t>
+          <t xml:space="preserve">0863726</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">태안　중앙　　　　　　　　　　</t>
+          <t xml:space="preserve">김해시민금고진영１지점　　　　</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  267  3894 </t>
+          <t xml:space="preserve">055  343  9700 </t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  267  3898 </t>
+          <t xml:space="preserve">055  343  9705 </t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">18391 </t>
+          <t xml:space="preserve">50865 </t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260527</t>
+          <t xml:space="preserve">20260601</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　화성시　병점구　병점중앙로　１９５　２０１호（진안동，　창현빌딩）　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　김해시　진영읍　여래로　２２　김해시민새마을금고　진영지점　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -6180,42 +6180,42 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t xml:space="preserve">0155256</t>
+          <t xml:space="preserve">2180892</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">ＫＢ증권　　　　　　</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">태안　기산　　　　　　　　　　</t>
+          <t xml:space="preserve">전북혁신도시라운지　　　　　　</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  221  3066 </t>
+          <t xml:space="preserve">063  916  7400 </t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  221  3098 </t>
+          <t xml:space="preserve">063  916  7499 </t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">18385 </t>
+          <t xml:space="preserve">54871 </t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260527</t>
+          <t xml:space="preserve">20260601</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　화성시　병점구　효행로　１１６１　대림프라자　２０３호　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전북특별자치도　전주시　덕진구　안전로　１４４　，　１층　（중동，엔씨빌딩）　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -6232,42 +6232,42 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t xml:space="preserve">0180865</t>
+          <t xml:space="preserve">2701103</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">하나증권　　　　　　</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">태안　서동탄역　　　　　　　　</t>
+          <t xml:space="preserve">ＴＨＥ　Ｈ１　Ｗ　　　　　　　</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  8015 2344 </t>
+          <t xml:space="preserve">02   2694 5282 </t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  8015 2349 </t>
+          <t xml:space="preserve">02   2694 5715 </t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">18429 </t>
+          <t xml:space="preserve">07998 </t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260527</t>
+          <t xml:space="preserve">20260601</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　화성시　동탄구　１０용사로　３４３－２　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　양천구　목동동로　２５７　（목동，　현대하이페리온），　６층　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -6279,12 +6279,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t xml:space="preserve">0182012</t>
+          <t xml:space="preserve">0185307</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -6294,32 +6294,32 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">태안농협　능동　　　　　　　　</t>
+          <t xml:space="preserve">　광혜원　화랑　　　　　　　　</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  234  1100 </t>
+          <t xml:space="preserve">043  000  0000 </t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  237  9912 </t>
+          <t xml:space="preserve">043  000  0000 </t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">18421 </t>
+          <t xml:space="preserve">27805 </t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260527</t>
+          <t xml:space="preserve">20260529</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　화성시　병점구　동탄지성로　１６６　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">충청북도　진천군　광혜원면　장기길　９１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -6331,99 +6331,99 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t xml:space="preserve">0374820</t>
+          <t xml:space="preserve">0454601</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">전북　　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">오토금융센터　　　　　　　　　</t>
+          <t xml:space="preserve">부산동구　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   1522 0034 </t>
+          <t xml:space="preserve">051  633  5743 </t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3145 4105 </t>
+          <t xml:space="preserve">051  633  5752 </t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">04034 </t>
+          <t xml:space="preserve">48735 </t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260527</t>
+          <t xml:space="preserve">20260528</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　마포구　양화로　８５　동현빌딩　８층　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">부산광역시　동구　범일로　１０１－８　（범일동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t xml:space="preserve">0374817</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t xml:space="preserve">0781442</t>
+          <t xml:space="preserve">0874016</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＫＢ국민　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">고객컨택영업２전주　　　　　　</t>
+          <t xml:space="preserve">애플금고　칠금지점　　　　　　</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800 9999 0000 </t>
+          <t xml:space="preserve">043  845  4501 </t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800 9999 0000 </t>
+          <t xml:space="preserve">043  845  4503 </t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">54871 </t>
+          <t xml:space="preserve">27354 </t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260527</t>
+          <t xml:space="preserve">20260528</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">전북특별자치도　전주시　덕진구　안전로　１４４　（중동）　５층　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">충청북도　충주시　번영대로　１６　（칠금동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -6440,42 +6440,42 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t xml:space="preserve">0113874</t>
+          <t xml:space="preserve">0143064</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">작전동　　　　　　　　　　　　</t>
+          <t xml:space="preserve">송산　사강　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">032  552  4121 </t>
+          <t xml:space="preserve">031  357  6800 </t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">032  552  0437 </t>
+          <t xml:space="preserve">031  357  6880 </t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">21120 </t>
+          <t xml:space="preserve">18550 </t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260526</t>
+          <t xml:space="preserve">20260527</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">인천광역시　계양구　계양대로　４４　（작전동），　덕용프라자　５０１호　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　화성시　만세구　송산면　사강로　１８８　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -6487,50 +6487,518 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
+          <t xml:space="preserve">변경    </t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0143077</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">농축협　　　　　　　</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">태안　안녕　　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">031  236  3301 </t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">031  236  3002 </t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18362 </t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20260527</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">경기도　화성시　병점구　용주로　２２　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       </t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">변경    </t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0146281</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">농축협　　　　　　　</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">한국화훼농협　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">031  910  8001 </t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">031  910  8010 </t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10226 </t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20260527</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">경기도　고양시　일산서구　대화로　３６２　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       </t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">변경    </t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0155227</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">농축협　　　　　　　</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">태안　중앙　　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">031  267  3894 </t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">031  267  3898 </t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18391 </t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20260527</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">경기도　화성시　병점구　병점중앙로　１９５　２０１호（진안동，　창현빌딩）　　　　　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       </t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">변경    </t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0155256</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">농축협　　　　　　　</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">태안　기산　　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">031  221  3066 </t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">031  221  3098 </t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18385 </t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20260527</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">경기도　화성시　병점구　효행로　１１６１　대림프라자　２０３호　　　　　　　　　　　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       </t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">변경    </t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0180865</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">농축협　　　　　　　</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">태안　서동탄역　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">031  8015 2344 </t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">031  8015 2349 </t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18429 </t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20260527</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">경기도　화성시　동탄구　１０용사로　３４３－２　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       </t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">변경    </t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0182012</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">농축협　　　　　　　</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">태안농협　능동　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">031  234  1100 </t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">031  237  9912 </t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18421 </t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20260527</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">경기도　화성시　병점구　동탄지성로　１６６　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       </t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">폐쇄    </t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0374820</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전북　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">오토금융센터　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02   1522 0034 </t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02   3145 4105 </t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04034 </t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20260527</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서울특별시　마포구　양화로　８５　동현빌딩　８층　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0374817</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
           <t xml:space="preserve">신규    </t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
+      <c r="B132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0781442</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ＫＢ국민　　　　　　</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">고객컨택영업２전주　　　　　　</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1800 9999 0000 </t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1800 9999 0000 </t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54871 </t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20260527</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전북특별자치도　전주시　덕진구　안전로　１４４　（중동）　５층　　　　　　　　　　　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       </t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">변경    </t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0113874</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작전동　　　　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">032  552  4121 </t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">032  552  0437 </t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21120 </t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20260526</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">인천광역시　계양구　계양대로　４４　（작전동），　덕용프라자　５０１호　　　　　　　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       </t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규    </t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
         <is>
           <t xml:space="preserve">0808406</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
+      <c r="C134" t="inlineStr">
         <is>
           <t xml:space="preserve">하나　　　　　　　　</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
+      <c r="D134" t="inlineStr">
         <is>
           <t xml:space="preserve">글로벌증권관리팀　　　　　　　</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
+      <c r="E134" t="inlineStr">
         <is>
           <t xml:space="preserve">02   729  0500 </t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
+      <c r="F134" t="inlineStr">
         <is>
           <t xml:space="preserve">02   2002 1465 </t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
+      <c r="G134" t="inlineStr">
         <is>
           <t xml:space="preserve">04538 </t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
+      <c r="H134" t="inlineStr">
         <is>
           <t xml:space="preserve">20260526</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr">
+      <c r="I134" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시　중구　을지로　６６　（을지로２가）　하나금융그룹명동사옥　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
-      <c r="J125" t="inlineStr">
+      <c r="J134" t="inlineStr">
         <is>
           <t xml:space="preserve">       </t>
         </is>

--- a/src/test/resources/codechgfile.text.xlsx
+++ b/src/test/resources/codechgfile.text.xlsx
@@ -34,7 +34,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J134"/>
+  <dimension ref="A1:J149"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -96,42 +96,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0070182</t>
+          <t xml:space="preserve">0027708</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">수협은행　　　　　　</t>
+          <t xml:space="preserve">산업　　　　　　　　</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">여신관리센터　　　　　　　　　</t>
+          <t xml:space="preserve">대구（지）　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   6055 7877 </t>
+          <t xml:space="preserve">053  606  2500 </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   418  7771 </t>
+          <t xml:space="preserve">053  255  1460 </t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">05542 </t>
+          <t xml:space="preserve">41585 </t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260624</t>
+          <t xml:space="preserve">20260629</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　송파구　올림픽로　３４０　５층（방이동　대동빌딩）　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">대구광역시　동구　동부로　１４０，　１０１동　３층（신천동，　ｅ편한세상　동대구역　센텀스퀘어　상가</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -143,104 +143,104 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0324003</t>
+          <t xml:space="preserve">0063966</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">부산　　　　　　　　</t>
+          <t xml:space="preserve">ＫＢ국민　　　　　　</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">복합지원센터　　　　　　　　　</t>
+          <t xml:space="preserve">서부지역영업그룹　　　　　　　</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">051  248  3967 </t>
+          <t xml:space="preserve">02   3156 5822 </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">051  608  5240 </t>
+          <t xml:space="preserve">02   3156 5898 </t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48955 </t>
+          <t xml:space="preserve">04027 </t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260623</t>
+          <t xml:space="preserve">20260629</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">부산광역시　중구　중앙대로　２１　（중앙동６가）　부산데파트　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　마포구　양화로　１９　（합정동）　합정오피스빌딩　１５층　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0036618</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">잠정패쇄</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0472900</t>
+          <t xml:space="preserve">0073710</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">신협　　　　　　　　</t>
+          <t xml:space="preserve">수협은행　　　　　　</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">제주신협　동문지점　　　　　　</t>
+          <t xml:space="preserve">인천수협　서창동지점　　　　　</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">064  752  5101 </t>
+          <t xml:space="preserve">032  465  1741 </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">064  758  0589 </t>
+          <t xml:space="preserve">032  465  1744 </t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">63264 </t>
+          <t xml:space="preserve">21602 </t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260623</t>
+          <t xml:space="preserve">20260629</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">제주특별자치도　제주시　동문로　４　（일도일동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">인천광역시　남동구　매소홀로　１１３７（서창동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0693718</t>
         </is>
       </c>
     </row>
@@ -252,42 +252,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">0487584</t>
+          <t xml:space="preserve">0110136</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">신협　　　　　　　　</t>
+          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">청주드림신협　문화센터지점　　</t>
+          <t xml:space="preserve">태평로금융센터　　　　　　　　</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  233  8100 </t>
+          <t xml:space="preserve">02   755  8255 </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  233  8103 </t>
+          <t xml:space="preserve">02   773  3836 </t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">28362 </t>
+          <t xml:space="preserve">04513 </t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260623</t>
+          <t xml:space="preserve">20260629</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">충청북도　청주시　흥덕구　２순환로　１０９８　（비하동）　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　중구　서소문로　１１６　（서소문동），　２층（유원빌딩）　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -304,42 +304,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">0494988</t>
+          <t xml:space="preserve">0116295</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">신협　　　　　　　　</t>
+          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">제주신협　　　　　　　　　　　</t>
+          <t xml:space="preserve">여수시（지부）　　　　　　　　</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">064  721  5101 </t>
+          <t xml:space="preserve">061  662  7121 </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 081  1013 </t>
+          <t xml:space="preserve">061  662  3270 </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">63234 </t>
+          <t xml:space="preserve">59752 </t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260623</t>
+          <t xml:space="preserve">20260629</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">제주특별자치도　제주시　연북로　５１７　（아라일동）　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전라남도　여수시　좌수영로　５４　（서교동）　중해마루힐아너스　상가동　１층　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -351,203 +351,203 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">0497257</t>
+          <t xml:space="preserve">0194932</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">신협　　　　　　　　</t>
+          <t xml:space="preserve">ＫＢ국민　　　　　　</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">제주신협　일도지점　　　　　　</t>
+          <t xml:space="preserve">북부지역영업그룹　　　　　　　</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">064  752  5102 </t>
+          <t xml:space="preserve">02   958  4425 </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">064  752  8388 </t>
+          <t xml:space="preserve">02   958  4440 </t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">63275 </t>
+          <t xml:space="preserve">01762 </t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260623</t>
+          <t xml:space="preserve">20260629</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">제주특별자치도　제주시　고마로　１０４　（일도이동）　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　노원구　동일로　１４０５　（상계동）　１５층　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0063319</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0860907</t>
+          <t xml:space="preserve">0194945</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">ＫＢ국민　　　　　　</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">명동금고시청역지점　　　　　　</t>
+          <t xml:space="preserve">경기지역영업그룹　　　　　　　</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   755  0038 </t>
+          <t xml:space="preserve">031  548  5500 </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   778  1980 </t>
+          <t xml:space="preserve">031  548  5599 </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">04526 </t>
+          <t xml:space="preserve">16897 </t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260623</t>
+          <t xml:space="preserve">20260629</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　중구　세종대로　８４　（태평로２가）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기　용인시　기흥구　죽전로　１５，　８층　（보정동，벤포스타Ⅱ빌딩）　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0194495</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">0872788</t>
+          <t xml:space="preserve">0195025</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">ＫＢ국민　　　　　　</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">대연금고　남광지점　　　　　　</t>
+          <t xml:space="preserve">강서지역영업그룹　　　　　　　</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">051  624  5800 </t>
+          <t xml:space="preserve">02   6980 9510 </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">051  714  0108 </t>
+          <t xml:space="preserve">02   6980 9514 </t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">48532 </t>
+          <t xml:space="preserve">07760 </t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260623</t>
+          <t xml:space="preserve">20260629</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">부산시　남구　흥곡로　３６０　대연금고　남광지점　상가　４０２동　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울　강서구　곰달래로　１３３　（화곡동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0063335</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877754</t>
+          <t xml:space="preserve">0232247</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">ＳＣ제일　　　　　　</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">경산금고　정평역지점　　　　　</t>
+          <t xml:space="preserve">올림픽파크포레온　　　　　　　</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  716  7517 </t>
+          <t xml:space="preserve">02   424  6705 </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  716  7518 </t>
+          <t xml:space="preserve">02   413  8298 </t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">38653 </t>
+          <t xml:space="preserve">05409 </t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260623</t>
+          <t xml:space="preserve">20260629</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상북도　경산시　성동로　２　（정평동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　강동구　양재대로　１３６０　（둔촌동）　포레온스테이션５　１층　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -559,359 +559,359 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">0030274</t>
+          <t xml:space="preserve">0376190</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">기업　　　　　　　　</t>
+          <t xml:space="preserve">전북　　　　　　　　</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">성수동（지）　　　　　　　　　</t>
+          <t xml:space="preserve">원광보건대영업점　　　　　　　</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   499  8001 </t>
+          <t xml:space="preserve">063  857  7851 </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 075  0027 </t>
+          <t xml:space="preserve">063  857  7853 </t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">04782 </t>
+          <t xml:space="preserve">54536 </t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260622</t>
+          <t xml:space="preserve">20260629</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　성동구　광나루로６길　１４　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전북특별자치도　익산시　익산대로　５０１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0376103</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">0113874</t>
+          <t xml:space="preserve">0376200</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
+          <t xml:space="preserve">전북　　　　　　　　</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">작전동　　　　　　　　　　　　</t>
+          <t xml:space="preserve">원광대영업점　　　　　　　　　</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">032  552  4121 </t>
+          <t xml:space="preserve">063  858  7338 </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">032  552  0437 </t>
+          <t xml:space="preserve">063  858  7339 </t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">21120 </t>
+          <t xml:space="preserve">54538 </t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260622</t>
+          <t xml:space="preserve">20260629</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">인천광역시　계양구　계양대로　４０　（작전동），　１층　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전북특별자치도　익산시　익산대로　４６０　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0376103</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">0203881</t>
+          <t xml:space="preserve">0504234</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">우리은행　　　　　　</t>
+          <t xml:space="preserve">저축은행　　　　　　</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">인하스카이지점　　　　　　　　</t>
+          <t xml:space="preserve">우리금융　　을지로（지）　　　</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">032  831  6321 </t>
+          <t xml:space="preserve">02   3459 6000 </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 001  3388 </t>
+          <t xml:space="preserve">02   3459 6040 </t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">22188 </t>
+          <t xml:space="preserve">04534 </t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260622</t>
+          <t xml:space="preserve">20260629</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">인천광역시　미추홀구　용정공원로８３번길　５９　（용현동）　３층　３０２호　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　중구　을지로　５０，　３층　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0504276</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">0231277</t>
+          <t xml:space="preserve">0692162</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＳＣ제일　　　　　　</t>
+          <t xml:space="preserve">수협중앙회　　　　　</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">장사동（지）　　　　　　　　　</t>
+          <t xml:space="preserve">인천수협　산곡지점　　　　　　</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2265 4101 </t>
+          <t xml:space="preserve">032  513  8335 </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2278 9793 </t>
+          <t xml:space="preserve">032  511  2865 </t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">110430</t>
+          <t xml:space="preserve">21376 </t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260622</t>
+          <t xml:space="preserve">20260629</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울　종로구　장사동　２０７의１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">인천광역시　부평구　마장로　３１４，　１층　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t xml:space="preserve">0231086</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">잠정패쇄</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">0232807</t>
+          <t xml:space="preserve">0693718</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＳＣ제일　　　　　　</t>
+          <t xml:space="preserve">수협중앙회　　　　　</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">남가좌동（지）　　　　　　　　</t>
+          <t xml:space="preserve">인천수협　서창동지점　　　　　</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   304  1091 </t>
+          <t xml:space="preserve">032  465  1741 </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   308  7452 </t>
+          <t xml:space="preserve">032  465  1744 </t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">03670 </t>
+          <t xml:space="preserve">21602 </t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260622</t>
+          <t xml:space="preserve">20260629</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울　서대문구　증가로１５０　ＤＭＣ　아이파크아파트상가２층　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">인천광역시　남동구　매소홀로　１１３７（서창동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve">0232784</t>
+          <t xml:space="preserve">0693718</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">0235037</t>
+          <t xml:space="preserve">0801254</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＳＣ제일　　　　　　</t>
+          <t xml:space="preserve">하나　　　　　　　　</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">범일동（지）　　　　　　　　　</t>
+          <t xml:space="preserve">서면역금융센터　　　　　　　　</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">051  646  5173 </t>
+          <t xml:space="preserve">051  807  1033 </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">051  643  7732 </t>
+          <t xml:space="preserve">051  808  7734 </t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">48738 </t>
+          <t xml:space="preserve">47254 </t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260622</t>
+          <t xml:space="preserve">20260629</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">부산광역시　동구　조방로　３９　２층　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">부산　부산진구　중앙대로　７４３　（부전동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve">0235040</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">0235040</t>
+          <t xml:space="preserve">2698274</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＳＣ제일　　　　　　</t>
+          <t xml:space="preserve">한화투자증권　　　　</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">부산서면ＷＭ센터　　　　　　　</t>
+          <t xml:space="preserve">연금상담센터　　　　　　　　　</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">051  802  5321 </t>
+          <t xml:space="preserve">080  851  7500 </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">051  816  0401 </t>
+          <t xml:space="preserve">02   3789 3879 </t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">47245 </t>
+          <t xml:space="preserve">04527 </t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260622</t>
+          <t xml:space="preserve">20260629</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">부산광역시　부산진구　중앙대로　７３６　（부전동）　경암센터　１층　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　중구　퇴계로　２５　（남대문로５가）　４층　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -923,208 +923,208 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">0805072</t>
+          <t xml:space="preserve">2703619</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나　　　　　　　　</t>
+          <t xml:space="preserve">하나증권　　　　　　</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">한겨레（출）　　　　　　　　　</t>
+          <t xml:space="preserve">미금역　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   703  1111 </t>
+          <t xml:space="preserve">031  716  3111 </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   704  9199 </t>
+          <t xml:space="preserve">031  716  3110 </t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">04186 </t>
+          <t xml:space="preserve">463805</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260622</t>
+          <t xml:space="preserve">20260629</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울　마포구　효창목길　６　（공덕동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　성남시　분당구　돌마로　６７　３층　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">2703619</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">잠정패쇄</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">0156679</t>
+          <t xml:space="preserve">0071699</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">수협은행　　　　　　</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">태안　반월　　　　　　　　　　</t>
+          <t xml:space="preserve">인천수협　작전동지점　　　　　</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  273  7859 </t>
+          <t xml:space="preserve">032  542  3361 </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  273  7863 </t>
+          <t xml:space="preserve">032  541  4475 </t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">18380 </t>
+          <t xml:space="preserve">21087 </t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260619</t>
+          <t xml:space="preserve">20260626</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　화성시　병점구　영통로　１４－１０　１０５호（반월동，토마토프라자）　　　　　　　　　　　　</t>
+          <t xml:space="preserve">인천광역시　계양구　주부토로　４６１（작전동）　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0691697</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">잠정패쇄</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">0734062</t>
+          <t xml:space="preserve">0691697</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">우체국　　　　　　　</t>
+          <t xml:space="preserve">수협중앙회　　　　　</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">홍성우체국　　　　　　　　　　</t>
+          <t xml:space="preserve">인천수협　작전동지점　　　　　</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">041  632  2014 </t>
+          <t xml:space="preserve">032  542  3361 </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">041  633  2006 </t>
+          <t xml:space="preserve">032  541  4475 </t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">32247 </t>
+          <t xml:space="preserve">21087 </t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260619</t>
+          <t xml:space="preserve">20260626</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">충청남도　홍성군　홍성읍　내포로　１１１　（홍성읍，홍성우체국）　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">인천광역시　계양구　주부토로　４６１（작전동）　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0691697</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">잠정패쇄</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">0746623</t>
+          <t xml:space="preserve">0691956</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">우체국　　　　　　　</t>
+          <t xml:space="preserve">수협중앙회　　　　　</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">광주오치동우체국　　　　　　　</t>
+          <t xml:space="preserve">인천수협　계산동지점　　　　　</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">062  264  2704 </t>
+          <t xml:space="preserve">032  542  3361 </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">062  267  1375 </t>
+          <t xml:space="preserve">032  541  4475 </t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">61122 </t>
+          <t xml:space="preserve">21087 </t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260619</t>
+          <t xml:space="preserve">20260626</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">광주광역시　북구　서하로　２４１　（오치동，오치동우체국）　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">인천광역시　계양구　주부토로　４６１（작전동）　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0691697</t>
         </is>
       </c>
     </row>
@@ -1136,42 +1136,42 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">0748333</t>
+          <t xml:space="preserve">0877178</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">우체국　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">금융원２지급센터　　　　　　　</t>
+          <t xml:space="preserve">지저금고　불로지점　　　　　　</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">062  375  7430 </t>
+          <t xml:space="preserve">053  981  5551 </t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">               </t>
+          <t xml:space="preserve">053  981  6037 </t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">61947 </t>
+          <t xml:space="preserve">41035 </t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260619</t>
+          <t xml:space="preserve">20260626</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">광주광역시　서구　상무중앙로　１１０　（치평동，우체국보험광주회관）　４층　청구심사２팀　　　　　　</t>
+          <t xml:space="preserve">대구광역시　동구　팔공로　１２７　（불로동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1183,47 +1183,47 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">4920021</t>
+          <t xml:space="preserve">0877181</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">중소벤처기업진흥공단</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">본사　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">지저금고　이시아지점　　　　　</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  751  9607 </t>
+          <t xml:space="preserve">053  981  5552 </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 047  4414 </t>
+          <t xml:space="preserve">053  984  7627 </t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">52851 </t>
+          <t xml:space="preserve">41026 </t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260619</t>
+          <t xml:space="preserve">20260626</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　동진로　４３０　（충무공동）　대출관리실　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">대구광역시　동구　팔공로５１길　３　（봉무동）　１０５호　１０６호　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1235,151 +1235,151 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">잠정패쇄</t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">0183176</t>
+          <t xml:space="preserve">0877767</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">일산　풍산역　　　　　　　　　</t>
+          <t xml:space="preserve">연수금고　선학지점　　　　　　</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  977  8062 </t>
+          <t xml:space="preserve">032  814  6414 </t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  977  8063 </t>
+          <t xml:space="preserve">032  811  2332 </t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">10355 </t>
+          <t xml:space="preserve">21909 </t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260618</t>
+          <t xml:space="preserve">20260626</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　고양시　일산동구　중산로　６３　현대프라자　２０１호　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">인천광역시　연수구　학나래로１１８번길　９　（선학동）　선학프라자　１０５호　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t xml:space="preserve">0122409</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">0390231</t>
+          <t xml:space="preserve">0877770</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">경남　　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">통합제도부　　　　　　　　　　</t>
+          <t xml:space="preserve">연수금고　문학지점　　　　　　</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  290  8381 </t>
+          <t xml:space="preserve">032  429  5501 </t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 082  6067 </t>
+          <t xml:space="preserve">032  429  5504 </t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">51316 </t>
+          <t xml:space="preserve">22235 </t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260618</t>
+          <t xml:space="preserve">20260626</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　창원시　마산회원구　３·１５대로　６４２　（석전동）　６４２　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">인천광역시　미추홀구　매소홀로　５４０　（문학동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t xml:space="preserve">0390671</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">0390532</t>
+          <t xml:space="preserve">2690845</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">경남　　　　　　　　</t>
+          <t xml:space="preserve">한화투자증권　　　　</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">디지털전략부　　　　　　　　　</t>
+          <t xml:space="preserve">ＰＬＵＳ자산관리센터　　　　　</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  290  8000 </t>
+          <t xml:space="preserve">02   3772 7288 </t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  290  8993 </t>
+          <t xml:space="preserve">02   3772 7298 </t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">630807</t>
+          <t xml:space="preserve">07345 </t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260618</t>
+          <t xml:space="preserve">20260626</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　창원시　마산회원구　３·１５대로　６４２　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　영등포구　６３로　５０　（여의도동）　ＰＬＵＳ자산관리센터　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1396,42 +1396,42 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">0390862</t>
+          <t xml:space="preserve">0072355</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">경남　　　　　　　　</t>
+          <t xml:space="preserve">수협은행　　　　　　</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">비대면마케팅부　　　　　　　　</t>
+          <t xml:space="preserve">수산해양금융부　　　　　　　　</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  290  8000 </t>
+          <t xml:space="preserve">02   6055 8510 </t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  290  8000 </t>
+          <t xml:space="preserve">02   3431 5220 </t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">51316 </t>
+          <t xml:space="preserve">05542 </t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260618</t>
+          <t xml:space="preserve">20260625</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　창원시　마산회원구　３·１５대로　６４２（석전동）　디지털마케팅부　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　송파구　올림픽로　３４０，　６층（방이동，대동빌딩）　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1443,52 +1443,52 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">0391942</t>
+          <t xml:space="preserve">0078883</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">경남　　　　　　　　</t>
+          <t xml:space="preserve">수협은행　　　　　　</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">윤리경영부　　　　　　　　　　</t>
+          <t xml:space="preserve">금융소비자보호본부　　　　　　</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  1588 8585 </t>
+          <t xml:space="preserve">02   6055 7610 </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 082  5300 </t>
+          <t xml:space="preserve">02   412  6403 </t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">51316 </t>
+          <t xml:space="preserve">05510 </t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260618</t>
+          <t xml:space="preserve">20260625</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　창원시　마산회원구　３·１５대로　６４２　（석전동）　윤리경영부　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　송파구　오금로　５８，　잠실아이스페이스　３층　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">0391955</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">0465865</t>
+          <t xml:space="preserve">0871792</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1510,32 +1510,32 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">우성　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">하남금고미사지점　　　　　　　</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  744  5551 </t>
+          <t xml:space="preserve">031  792  2716 </t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  744  5552 </t>
+          <t xml:space="preserve">070  4015 0645 </t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">38076 </t>
+          <t xml:space="preserve">12909 </t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260618</t>
+          <t xml:space="preserve">20260625</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상북도　경주시　유림로　１０７　（용강동，　두산위브트레지움）　근린생활시설２동　２０３호　　　　</t>
+          <t xml:space="preserve">경기　하남시　미사강변대로　２０６　리더스프라자　２층　하남새마을금고　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1547,312 +1547,312 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">0502155</t>
+          <t xml:space="preserve">0070182</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">저축은행　　　　　　</t>
+          <t xml:space="preserve">수협은행　　　　　　</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">유니온　　　기업금융관리팀　　</t>
+          <t xml:space="preserve">여신관리센터　　　　　　　　　</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  256  4000 </t>
+          <t xml:space="preserve">02   6055 7877 </t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  255  8709 </t>
+          <t xml:space="preserve">02   418  7771 </t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">41951 </t>
+          <t xml:space="preserve">05542 </t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260618</t>
+          <t xml:space="preserve">20260624</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">대구광역시　중구　달구벌대로　２２１０　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　송파구　올림픽로　３４０　５층（방이동　대동빌딩）　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">0502087</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">0502184</t>
+          <t xml:space="preserve">0324003</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">저축은행　　　　　　</t>
+          <t xml:space="preserve">부산　　　　　　　　</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">유니온　　　오토금융팀　　　　</t>
+          <t xml:space="preserve">복합지원센터　　　　　　　　　</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  256  4000 </t>
+          <t xml:space="preserve">051  248  3967 </t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  256  4006 </t>
+          <t xml:space="preserve">051  608  5240 </t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">41935 </t>
+          <t xml:space="preserve">48955 </t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260618</t>
+          <t xml:space="preserve">20260623</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">대구광역시　중구　국채보상로　５７０　－１，　유니온저축은행　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">부산광역시　중구　중앙대로　２１　（중앙동６가）　부산데파트　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">0502087</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">0502197</t>
+          <t xml:space="preserve">0472900</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">저축은행　　　　　　</t>
+          <t xml:space="preserve">신협　　　　　　　　</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">유니온　　　기업금융１팀　　　</t>
+          <t xml:space="preserve">제주신협　동문지점　　　　　　</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  256  4000 </t>
+          <t xml:space="preserve">064  752  5101 </t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  256  4006 </t>
+          <t xml:space="preserve">064  758  0589 </t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">41935 </t>
+          <t xml:space="preserve">63264 </t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260618</t>
+          <t xml:space="preserve">20260623</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">대구광역시　중구　국채보상로　５７０－１　유니온저축은행　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">제주특별자치도　제주시　동문로　４　（일도일동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t xml:space="preserve">0502087</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">0502207</t>
+          <t xml:space="preserve">0487584</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">저축은행　　　　　　</t>
+          <t xml:space="preserve">신협　　　　　　　　</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">유니온　　　전략영업１팀　　　</t>
+          <t xml:space="preserve">청주드림신협　문화센터지점　　</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  256  4000 </t>
+          <t xml:space="preserve">043  233  8100 </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  255  8709 </t>
+          <t xml:space="preserve">043  233  8103 </t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">41951 </t>
+          <t xml:space="preserve">28362 </t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260618</t>
+          <t xml:space="preserve">20260623</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">대구광역시　중구　달구벌대로　２２１０　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">충청북도　청주시　흥덕구　２순환로　１０９８　（비하동）　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve">0502087</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">0502210</t>
+          <t xml:space="preserve">0494988</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">저축은행　　　　　　</t>
+          <t xml:space="preserve">신협　　　　　　　　</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">유니온　　　전략영업３팀　　　</t>
+          <t xml:space="preserve">제주신협　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  256  4000 </t>
+          <t xml:space="preserve">064  721  5101 </t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  423  3009 </t>
+          <t xml:space="preserve">0505 081  1013 </t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">41951 </t>
+          <t xml:space="preserve">63234 </t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260618</t>
+          <t xml:space="preserve">20260623</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">대구광역시　중구　달구벌대로　２２１０　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">제주특별자치도　제주시　연북로　５１７　（아라일동）　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve">0502087</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">0509459</t>
+          <t xml:space="preserve">0497257</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">저축은행　　　　　　</t>
+          <t xml:space="preserve">신협　　　　　　　　</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">유니온　　　본부　　　　　　　</t>
+          <t xml:space="preserve">제주신협　일도지점　　　　　　</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  256  4000 </t>
+          <t xml:space="preserve">064  752  5102 </t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  256  4000 </t>
+          <t xml:space="preserve">064  752  8388 </t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">41935 </t>
+          <t xml:space="preserve">63275 </t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260618</t>
+          <t xml:space="preserve">20260623</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">대구광역시　중구　국채보상로　５７０－１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">제주특별자치도　제주시　고마로　１０４　（일도이동）　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t xml:space="preserve">0502087</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">0874346</t>
+          <t xml:space="preserve">0860907</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1874,32 +1874,32 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">우성새마을금고황오동지점　　　</t>
+          <t xml:space="preserve">명동금고시청역지점　　　　　　</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  777  5551 </t>
+          <t xml:space="preserve">02   755  0038 </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  777  5552 </t>
+          <t xml:space="preserve">02   778  1980 </t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">38159 </t>
+          <t xml:space="preserve">04526 </t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260618</t>
+          <t xml:space="preserve">20260623</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상북도　경주시　원효로　１４６　우성금고황오동지점　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　중구　세종대로　８４　（태평로２가）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -1916,42 +1916,42 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">0130941</t>
+          <t xml:space="preserve">0872788</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">태안　망포　　　　　　　　　　</t>
+          <t xml:space="preserve">대연금고　남광지점　　　　　　</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  205  1106 </t>
+          <t xml:space="preserve">051  624  5800 </t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  205  1107 </t>
+          <t xml:space="preserve">051  714  0108 </t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">16692 </t>
+          <t xml:space="preserve">48532 </t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260617</t>
+          <t xml:space="preserve">20260623</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　수원시　영통구　영통로９０번길　７　（망포동）　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">부산시　남구　흥곡로　３６０　대연금고　남광지점　상가　４０２동　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -1963,47 +1963,47 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">0133689</t>
+          <t xml:space="preserve">0877754</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">경주　내남　　　　　　　　　　</t>
+          <t xml:space="preserve">경산금고　정평역지점　　　　　</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  748  2641 </t>
+          <t xml:space="preserve">053  716  7517 </t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  748  3642 </t>
+          <t xml:space="preserve">053  716  7518 </t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">38193 </t>
+          <t xml:space="preserve">38653 </t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260617</t>
+          <t xml:space="preserve">20260623</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상북도　경주시　내남면　이조중앙길　１７　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상북도　경산시　성동로　２　（정평동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2020,42 +2020,42 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">0141367</t>
+          <t xml:space="preserve">0030274</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">기업　　　　　　　　</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">태안　기배　　　　　　　　　　</t>
+          <t xml:space="preserve">성수동（지）　　　　　　　　　</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  267  3245 </t>
+          <t xml:space="preserve">02   499  8001 </t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  267  3249 </t>
+          <t xml:space="preserve">0505 075  0027 </t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">18341 </t>
+          <t xml:space="preserve">04782 </t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260617</t>
+          <t xml:space="preserve">20260622</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　화성시　효행구　기안남로　７０　（기안동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　성동구　광나루로６길　１４　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2072,42 +2072,42 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">0155256</t>
+          <t xml:space="preserve">0113874</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">태안　기산　　　　　　　　　　</t>
+          <t xml:space="preserve">작전동　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  221  3066 </t>
+          <t xml:space="preserve">032  552  4121 </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  221  3098 </t>
+          <t xml:space="preserve">032  552  0437 </t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">18385 </t>
+          <t xml:space="preserve">21120 </t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260617</t>
+          <t xml:space="preserve">20260622</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　화성시　병점구　효행로　１１６１　２０３호（기산동，　대림프라자）　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">인천광역시　계양구　계양대로　４０　（작전동），　１층　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2124,42 +2124,42 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">0156077</t>
+          <t xml:space="preserve">0203881</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">우리은행　　　　　　</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">태안　구봉　　　　　　　　　　</t>
+          <t xml:space="preserve">인하스카이지점　　　　　　　　</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  225  7480 </t>
+          <t xml:space="preserve">032  831  6321 </t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  225  7484 </t>
+          <t xml:space="preserve">0505 001  3388 </t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">18409 </t>
+          <t xml:space="preserve">22188 </t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260617</t>
+          <t xml:space="preserve">20260622</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　화성시　병점구　병점２로　６９　（병점동，재성빌딩）　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">인천광역시　미추홀구　용정공원로８３번길　５９　（용현동）　３층　３０２호　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2171,156 +2171,156 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">0158910</t>
+          <t xml:space="preserve">0231277</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">ＳＣ제일　　　　　　</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">태안　태장　　　　　　　　　　</t>
+          <t xml:space="preserve">장사동（지）　　　　　　　　　</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  202  1801 </t>
+          <t xml:space="preserve">02   2265 4101 </t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  202  1866 </t>
+          <t xml:space="preserve">02   2278 9793 </t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">16685 </t>
+          <t xml:space="preserve">110430</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260617</t>
+          <t xml:space="preserve">20260622</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　수원시　영통구　덕영대로　１４７０　１１６호（망포동，　플래티넘베이스）　　　　　　　　　　</t>
+          <t xml:space="preserve">서울　종로구　장사동　２０７의１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0231086</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">0182012</t>
+          <t xml:space="preserve">0232807</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">ＳＣ제일　　　　　　</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">태안농협　능동　　　　　　　　</t>
+          <t xml:space="preserve">남가좌동（지）　　　　　　　　</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  234  1100 </t>
+          <t xml:space="preserve">02   304  1091 </t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  237  9912 </t>
+          <t xml:space="preserve">02   308  7452 </t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">18421 </t>
+          <t xml:space="preserve">03670 </t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260617</t>
+          <t xml:space="preserve">20260622</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　화성시　병점구　동탄지성로　１６６　（능동）　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울　서대문구　증가로１５０　ＤＭＣ　아이파크아파트상가２층　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0232784</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">0185297</t>
+          <t xml:space="preserve">0235037</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">ＳＣ제일　　　　　　</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">충북낙농　서현　　　　　　　　</t>
+          <t xml:space="preserve">범일동（지）　　　　　　　　　</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  233  5536 </t>
+          <t xml:space="preserve">051  646  5173 </t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  233  5538 </t>
+          <t xml:space="preserve">051  643  7732 </t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">28382 </t>
+          <t xml:space="preserve">48738 </t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260617</t>
+          <t xml:space="preserve">20260622</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">충청북도　청주시　흥덕구　서현남로　１６　１층　１１１호（가경동　６３９－１）　　　　　　　　　　　</t>
+          <t xml:space="preserve">부산광역시　동구　조방로　３９　２층　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0235040</t>
         </is>
       </c>
     </row>
@@ -2332,42 +2332,42 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">0861906</t>
+          <t xml:space="preserve">0235040</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">ＳＣ제일　　　　　　</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">신포항금고제１지점　　　　　　</t>
+          <t xml:space="preserve">부산서면ＷＭ센터　　　　　　　</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  281  3766 </t>
+          <t xml:space="preserve">051  802  5321 </t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  281  3770 </t>
+          <t xml:space="preserve">051  816  0401 </t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">37690 </t>
+          <t xml:space="preserve">47245 </t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260617</t>
+          <t xml:space="preserve">20260622</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상북도　포항시　북구　이동로　４７　（득량동）　삼구트리니엔시그니처　제　１３１동　１０２호　　　</t>
+          <t xml:space="preserve">부산광역시　부산진구　중앙대로　７３６　（부전동）　경암센터　１층　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2384,42 +2384,42 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">0873127</t>
+          <t xml:space="preserve">0805072</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">하나　　　　　　　　</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">중부금고지금지점　　　　　　　</t>
+          <t xml:space="preserve">한겨레（출）　　　　　　　　　</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  577  7771 </t>
+          <t xml:space="preserve">02   703  1111 </t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  521  9888 </t>
+          <t xml:space="preserve">02   704  9199 </t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">12284 </t>
+          <t xml:space="preserve">04186 </t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260617</t>
+          <t xml:space="preserve">20260622</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　남양주시　다산지금로　１４１　２층　중부금고　지금지점　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울　마포구　효창목길　６　（공덕동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2431,47 +2431,47 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877712</t>
+          <t xml:space="preserve">0156679</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">평화금고　송림지점　　　　　　</t>
+          <t xml:space="preserve">태안　반월　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">032  764  7081 </t>
+          <t xml:space="preserve">031  273  7859 </t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">032  777  2182 </t>
+          <t xml:space="preserve">031  273  7863 </t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">22570 </t>
+          <t xml:space="preserve">18380 </t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260617</t>
+          <t xml:space="preserve">20260619</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">인천광역시　동구　송림로１６２번길　１０　（송림동，　송림파인앤유）　１층　１１７호，　１１８호　　</t>
+          <t xml:space="preserve">경기도　화성시　병점구　영통로　１４－１０　１０５호（반월동，토마토프라자）　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2483,47 +2483,47 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877725</t>
+          <t xml:space="preserve">0734062</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">우체국　　　　　　　</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">평화금고　로타리지점　　　　　</t>
+          <t xml:space="preserve">홍성우체국　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">032  765  6688 </t>
+          <t xml:space="preserve">041  632  2014 </t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">032  765  6686 </t>
+          <t xml:space="preserve">041  633  2006 </t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">22543 </t>
+          <t xml:space="preserve">32247 </t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260617</t>
+          <t xml:space="preserve">20260619</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">인천광역시　동구　솔빛로９１번길　７　（송림동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">충청남도　홍성군　홍성읍　내포로　１１１　（홍성읍，홍성우체국）　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2535,47 +2535,47 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877738</t>
+          <t xml:space="preserve">0746623</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">우체국　　　　　　　</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">팔달금고　세화지점　　　　　　</t>
+          <t xml:space="preserve">광주오치동우체국　　　　　　　</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  236  9970 </t>
+          <t xml:space="preserve">062  264  2704 </t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  236  2106 </t>
+          <t xml:space="preserve">062  267  1375 </t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">16587 </t>
+          <t xml:space="preserve">61122 </t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260617</t>
+          <t xml:space="preserve">20260619</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　수원시　권선구　정조로　５３７　（세류동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">광주광역시　북구　서하로　２４１　（오치동，오치동우체국）　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2587,47 +2587,47 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877741</t>
+          <t xml:space="preserve">0748333</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">우체국　　　　　　　</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">팔달금고　권선지점　　　　　　</t>
+          <t xml:space="preserve">금융원２지급센터　　　　　　　</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  236  9975 </t>
+          <t xml:space="preserve">062  375  7430 </t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  234  7981 </t>
+          <t xml:space="preserve">               </t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">16589 </t>
+          <t xml:space="preserve">61947 </t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260617</t>
+          <t xml:space="preserve">20260619</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　수원시　권선구　세지로２８번길　４２　（세류동）　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">광주광역시　서구　상무중앙로　１１０　（치평동，우체국보험광주회관）　４층　청구심사２팀　　　　　　</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -2639,47 +2639,47 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">0701228</t>
+          <t xml:space="preserve">4920021</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">수협중앙회　　　　　</t>
+          <t xml:space="preserve">중소벤처기업진흥공단</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">거제수협　외대역금융센터　　　</t>
+          <t xml:space="preserve">본사　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   962  2280 </t>
+          <t xml:space="preserve">055  751  9607 </t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   962  2282 </t>
+          <t xml:space="preserve">0505 047  4414 </t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">02418 </t>
+          <t xml:space="preserve">52851 </t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260616</t>
+          <t xml:space="preserve">20260619</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　동대문구　이문로　１２０　（이문동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　진주시　동진로　４３０　（충무공동）　대출관리실　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -2691,104 +2691,104 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">잠정패쇄</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">0802525</t>
+          <t xml:space="preserve">0183176</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나　　　　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">골드클럽　올림픽선수촌ＰＢ센터</t>
+          <t xml:space="preserve">일산　풍산역　　　　　　　　　</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   406  6672 </t>
+          <t xml:space="preserve">031  977  8062 </t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   400  4069 </t>
+          <t xml:space="preserve">031  977  8063 </t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">05648 </t>
+          <t xml:space="preserve">10355 </t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260615</t>
+          <t xml:space="preserve">20260618</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울　송파구　양재대로　１２２２　（방이동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　고양시　일산동구　중산로　６３　현대프라자　２０１호　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0122409</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">0811639</t>
+          <t xml:space="preserve">0390231</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나　　　　　　　　</t>
+          <t xml:space="preserve">경남　　　　　　　　</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">화곡역금융센터　　　　　　　　</t>
+          <t xml:space="preserve">통합제도부　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2693 1111 </t>
+          <t xml:space="preserve">055  290  8381 </t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2607 0830 </t>
+          <t xml:space="preserve">0505 082  6067 </t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">157922</t>
+          <t xml:space="preserve">51316 </t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260615</t>
+          <t xml:space="preserve">20260618</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울　강서구　화곡３동　１０５１－１７번지　대사빌딩　１층　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　창원시　마산회원구　３·１５대로　６４２　（석전동）　６４２　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0390671</t>
         </is>
       </c>
     </row>
@@ -2800,42 +2800,42 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">0812366</t>
+          <t xml:space="preserve">0390532</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나　　　　　　　　</t>
+          <t xml:space="preserve">경남　　　　　　　　</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">골드클럽　아시아선수촌ＰＢ센터</t>
+          <t xml:space="preserve">디지털전략부　　　　　　　　　</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   472  1111 </t>
+          <t xml:space="preserve">055  290  8000 </t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   420  2322 </t>
+          <t xml:space="preserve">055  290  8993 </t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">138797</t>
+          <t xml:space="preserve">630807</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260615</t>
+          <t xml:space="preserve">20260618</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울　송파구　잠실７동　８５－１　아시아선수촌상가１층　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　창원시　마산회원구　３·１５대로　６４２　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -2852,42 +2852,42 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">0812816</t>
+          <t xml:space="preserve">0390862</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나　　　　　　　　</t>
+          <t xml:space="preserve">경남　　　　　　　　</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">왕십리금융센터　　　　　　　　</t>
+          <t xml:space="preserve">비대면마케팅부　　　　　　　　</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2294 1111 </t>
+          <t xml:space="preserve">055  290  8000 </t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2297 7181 </t>
+          <t xml:space="preserve">055  290  8000 </t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">133030</t>
+          <t xml:space="preserve">51316 </t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260615</t>
+          <t xml:space="preserve">20260618</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울시　성동구　홍익동　１２５　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　창원시　마산회원구　３·１５대로　６４２（석전동）　디지털마케팅부　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -2899,64 +2899,64 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">0819204</t>
+          <t xml:space="preserve">0391942</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나　　　　　　　　</t>
+          <t xml:space="preserve">경남　　　　　　　　</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">골드클럽　영업１부　ＰＢ센터　</t>
+          <t xml:space="preserve">윤리경영부　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   737  1111 </t>
+          <t xml:space="preserve">055  1588 8585 </t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   757  6692 </t>
+          <t xml:space="preserve">0505 082  5300 </t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">04523 </t>
+          <t xml:space="preserve">51316 </t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260615</t>
+          <t xml:space="preserve">20260618</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　중구　을지로　３５（을지로１가）　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　창원시　마산회원구　３·１５대로　６４２　（석전동）　윤리경영부　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0391955</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877699</t>
+          <t xml:space="preserve">0465865</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">동군산금고　양안금고　　　　　</t>
+          <t xml:space="preserve">우성　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  471  2442 </t>
+          <t xml:space="preserve">054  744  5551 </t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  451  4777 </t>
+          <t xml:space="preserve">054  744  5552 </t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">54074 </t>
+          <t xml:space="preserve">38076 </t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260615</t>
+          <t xml:space="preserve">20260618</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">전북특별자치도　군산시　부골１길　４７　（조촌동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상북도　경주시　유림로　１０７　（용강동，　두산위브트레지움）　근린생활시설２동　２０３호　　　　</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3003,312 +3003,312 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877709</t>
+          <t xml:space="preserve">0502155</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">저축은행　　　　　　</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">동군산금고　발산지점　　　　　</t>
+          <t xml:space="preserve">유니온　　　기업금융관리팀　　</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  451  4334 </t>
+          <t xml:space="preserve">053  256  4000 </t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  451  4774 </t>
+          <t xml:space="preserve">053  255  8709 </t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">54065 </t>
+          <t xml:space="preserve">41951 </t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260615</t>
+          <t xml:space="preserve">20260618</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">전북특별자치도　군산시　개정면　바르메길　３９　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">대구광역시　중구　달구벌대로　２２１０　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0502087</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2708504</t>
+          <t xml:space="preserve">0502184</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나증권　　　　　　</t>
+          <t xml:space="preserve">저축은행　　　　　　</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">전주　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">유니온　　　오토금융팀　　　　</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  276  1212 </t>
+          <t xml:space="preserve">053  256  4000 </t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  253  2033 </t>
+          <t xml:space="preserve">053  256  4006 </t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">54966 </t>
+          <t xml:space="preserve">41935 </t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260615</t>
+          <t xml:space="preserve">20260618</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">전북특별자치도　전주시　완산구　홍산로　２６１　（효자동２가），　ＢＹＣ건물　１층　　　　　　　　　</t>
+          <t xml:space="preserve">대구광역시　중구　국채보상로　５７０　－１，　유니온저축은행　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0502087</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">0459473</t>
+          <t xml:space="preserve">0502197</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">저축은행　　　　　　</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">나주동부　　　　　　　　　　　</t>
+          <t xml:space="preserve">유니온　　　기업금융１팀　　　</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  331  1557 </t>
+          <t xml:space="preserve">053  256  4000 </t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  331  5547 </t>
+          <t xml:space="preserve">053  256  4006 </t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">58227 </t>
+          <t xml:space="preserve">41935 </t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260612</t>
+          <t xml:space="preserve">20260618</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">전라남도　나주시　남평읍　강변１길　７３－１２　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">대구광역시　중구　국채보상로　５７０－１　유니온저축은행　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0502087</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">0874786</t>
+          <t xml:space="preserve">0502207</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">저축은행　　　　　　</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">소양강금고약사지점　　　　　　</t>
+          <t xml:space="preserve">유니온　　　전략영업１팀　　　</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">033  252  7559 </t>
+          <t xml:space="preserve">053  256  4000 </t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">033  252  7550 </t>
+          <t xml:space="preserve">053  255  8709 </t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">24357 </t>
+          <t xml:space="preserve">41951 </t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260612</t>
+          <t xml:space="preserve">20260618</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">강원특별자치도　춘천시　공지로　４００　－１００５　１층　１０６호　소양강금고　약사지점　　　　　　</t>
+          <t xml:space="preserve">대구광역시　중구　달구벌대로　２２１０　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0502087</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">0875235</t>
+          <t xml:space="preserve">0502210</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">저축은행　　　　　　</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">나주동부금고남평지점　　　　　</t>
+          <t xml:space="preserve">유니온　　　전략영업３팀　　　</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  336  1557 </t>
+          <t xml:space="preserve">053  256  4000 </t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  336  5547 </t>
+          <t xml:space="preserve">053  423  3009 </t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">58227 </t>
+          <t xml:space="preserve">41951 </t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260612</t>
+          <t xml:space="preserve">20260618</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">전라남도　나주시　남평읍　남평２로　４１－５　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">대구광역시　중구　달구벌대로　２２１０　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0502087</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">0805810</t>
+          <t xml:space="preserve">0509459</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나　　　　　　　　</t>
+          <t xml:space="preserve">저축은행　　　　　　</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">검단구청　　　　　　　　　　　</t>
+          <t xml:space="preserve">유니온　　　본부　　　　　　　</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">032  766  1111 </t>
+          <t xml:space="preserve">053  256  4000 </t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">032  262  1092 </t>
+          <t xml:space="preserve">053  256  4000 </t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">22679 </t>
+          <t xml:space="preserve">41935 </t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260611</t>
+          <t xml:space="preserve">20260618</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">인천광역시　서구　독정로１２５번길　１２　（당하동）　당하동　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">대구광역시　중구　국채보상로　５７０－１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0502087</t>
         </is>
       </c>
     </row>
@@ -3320,42 +3320,42 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">0121015</t>
+          <t xml:space="preserve">0874346</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">금왕농협　　　　　　　　　　　</t>
+          <t xml:space="preserve">우성새마을금고황오동지점　　　</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  877  0841 </t>
+          <t xml:space="preserve">054  777  5551 </t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">0503 8880 2300 </t>
+          <t xml:space="preserve">054  777  5552 </t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">27629 </t>
+          <t xml:space="preserve">38159 </t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260610</t>
+          <t xml:space="preserve">20260618</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">충청북도　음성군　금왕읍　무극로　２９３　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상북도　경주시　원효로　１４６　우성금고황오동지점　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">0144005</t>
+          <t xml:space="preserve">0130941</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3382,32 +3382,32 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">동부　낙서　　　　　　　　　　</t>
+          <t xml:space="preserve">태안　망포　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  572  7018 </t>
+          <t xml:space="preserve">031  205  1106 </t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">0503 8880 5630 </t>
+          <t xml:space="preserve">031  205  1107 </t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">52108 </t>
+          <t xml:space="preserve">16692 </t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260610</t>
+          <t xml:space="preserve">20260617</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　의령군　낙서면　낙서로　５２３　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　수원시　영통구　영통로９０번길　７　（망포동）　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">0150691</t>
+          <t xml:space="preserve">0133689</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3434,32 +3434,32 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">탕정　동산　　　　　　　　　　</t>
+          <t xml:space="preserve">경주　내남　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">041  534  1811 </t>
+          <t xml:space="preserve">054  748  2641 </t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">041  534  1904 </t>
+          <t xml:space="preserve">054  748  3642 </t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">31458 </t>
+          <t xml:space="preserve">38193 </t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260610</t>
+          <t xml:space="preserve">20260617</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">충청남도　아산시　탕정면　삼성로　４４０　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상북도　경주시　내남면　이조중앙길　１７　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3476,42 +3476,42 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">0850739</t>
+          <t xml:space="preserve">0141367</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">광양시금고마동지점　　　　　　</t>
+          <t xml:space="preserve">태안　기배　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  797  1490 </t>
+          <t xml:space="preserve">031  267  3245 </t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  795  8776 </t>
+          <t xml:space="preserve">031  267  3249 </t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">57778 </t>
+          <t xml:space="preserve">18341 </t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260610</t>
+          <t xml:space="preserve">20260617</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남　광양시　진등길　５５－５　송보５차상가내　５１０－２０２　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　화성시　효행구　기안남로　７０　（기안동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -3528,42 +3528,42 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">0043562</t>
+          <t xml:space="preserve">0155256</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＫＢ국민　　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">휘경동　　　　　　　　　　　　</t>
+          <t xml:space="preserve">태안　기산　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2215 0963 </t>
+          <t xml:space="preserve">031  221  3066 </t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2215 5040 </t>
+          <t xml:space="preserve">031  221  3098 </t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">02418 </t>
+          <t xml:space="preserve">18385 </t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260608</t>
+          <t xml:space="preserve">20260617</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　동대문구　이문로　１２０　（이문동），４１２－１번지　２층　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　화성시　병점구　효행로　１１６１　２０３호（기산동，　대림프라자）　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -3580,42 +3580,42 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">0105109</t>
+          <t xml:space="preserve">0156077</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">북의왕　　　　　　　　　　　　</t>
+          <t xml:space="preserve">태안　구봉　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  425  0432 </t>
+          <t xml:space="preserve">031  225  7480 </t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  425  0430 </t>
+          <t xml:space="preserve">031  225  7484 </t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">16024 </t>
+          <t xml:space="preserve">18409 </t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260608</t>
+          <t xml:space="preserve">20260617</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　의왕시　포일로　２０　（내손동）　래미안에버하임아파트　１층　상가　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　화성시　병점구　병점２로　６９　（병점동，재성빌딩）　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">0153818</t>
+          <t xml:space="preserve">0158910</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3642,32 +3642,32 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">태안　영통동　　　　　　　　　</t>
+          <t xml:space="preserve">태안　태장　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  204  3891 </t>
+          <t xml:space="preserve">031  202  1801 </t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  204  3895 </t>
+          <t xml:space="preserve">031  202  1866 </t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">16701 </t>
+          <t xml:space="preserve">16685 </t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260608</t>
+          <t xml:space="preserve">20260617</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　수원시　영통구　매영로　３６８　（영통동，　살구골현대아파트상가）　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　수원시　영통구　덕영대로　１４７０　１１６호（망포동，　플래티넘베이스）　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -3684,42 +3684,42 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">0804031</t>
+          <t xml:space="preserve">0182012</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나　　　　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">골드클럽　강남파이낸스ＰＢ센터</t>
+          <t xml:space="preserve">태안농협　능동　　　　　　　　</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   554  3076 </t>
+          <t xml:space="preserve">031  234  1100 </t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   562  5509 </t>
+          <t xml:space="preserve">031  237  9912 </t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">06236 </t>
+          <t xml:space="preserve">18421 </t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260608</t>
+          <t xml:space="preserve">20260617</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울　강남구　테헤란로　１５２　（역삼동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　화성시　병점구　동탄지성로　１６６　（능동）　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -3736,42 +3736,42 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">0805690</t>
+          <t xml:space="preserve">0185297</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나　　　　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">골드클럽　여의도ＰＢ센터　　　</t>
+          <t xml:space="preserve">충북낙농　서현　　　　　　　　</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   765  1111 </t>
+          <t xml:space="preserve">043  233  5536 </t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   784  8128 </t>
+          <t xml:space="preserve">043  233  5538 </t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">07339 </t>
+          <t xml:space="preserve">28382 </t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260608</t>
+          <t xml:space="preserve">20260617</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　브라이튼여의도　２층　　　</t>
+          <t xml:space="preserve">충청북도　청주시　흥덕구　서현남로　１６　１층　１１１호（가경동　６３９－１）　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -3788,42 +3788,42 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">0811451</t>
+          <t xml:space="preserve">0861906</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나　　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">골드클럽　평창동ＰＢ센터　　　</t>
+          <t xml:space="preserve">신포항금고제１지점　　　　　　</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   391  1111 </t>
+          <t xml:space="preserve">054  281  3766 </t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   395  8047 </t>
+          <t xml:space="preserve">054  281  3770 </t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">03009 </t>
+          <t xml:space="preserve">37690 </t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260608</t>
+          <t xml:space="preserve">20260617</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　종로구　평창문화로　８７　창진파크팰리스　１층　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상북도　포항시　북구　이동로　４７　（득량동）　삼구트리니엔시그니처　제　１３１동　１０２호　　　</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -3840,42 +3840,42 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">0814173</t>
+          <t xml:space="preserve">0873127</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나　　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">골드클럽　분당ＰＢ센터　　　　</t>
+          <t xml:space="preserve">중부금고지금지점　　　　　　　</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  779  1111 </t>
+          <t xml:space="preserve">031  577  7771 </t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  779  1222 </t>
+          <t xml:space="preserve">031  521  9888 </t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">463050</t>
+          <t xml:space="preserve">12284 </t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260608</t>
+          <t xml:space="preserve">20260617</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　성남시　분당구　서현동　２６５－２번지　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　남양주시　다산지금로　１４１　２층　중부금고　지금지점　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -3887,47 +3887,47 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">0815732</t>
+          <t xml:space="preserve">0877712</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나　　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">골드클럽　용산ＰＢ센터　　　　</t>
+          <t xml:space="preserve">평화금고　송림지점　　　　　　</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   797  1111 </t>
+          <t xml:space="preserve">032  764  7081 </t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   797  8795 </t>
+          <t xml:space="preserve">032  777  2182 </t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">140240</t>
+          <t xml:space="preserve">22570 </t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260608</t>
+          <t xml:space="preserve">20260617</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울시　용산구　서빙고동　２７１－１０６외　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">인천광역시　동구　송림로１６２번길　１０　（송림동，　송림파인앤유）　１층　１１７호，　１１８호　　</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -3939,47 +3939,47 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">0819178</t>
+          <t xml:space="preserve">0877725</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나　　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">골드클럽　압구정ＰＢ센터　　　</t>
+          <t xml:space="preserve">평화금고　로타리지점　　　　　</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   512  1111 </t>
+          <t xml:space="preserve">032  765  6688 </t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   542  9872 </t>
+          <t xml:space="preserve">032  765  6686 </t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">135894</t>
+          <t xml:space="preserve">22543 </t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260608</t>
+          <t xml:space="preserve">20260617</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울　강남구　신사동　６１８－３　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">인천광역시　동구　솔빛로９１번길　７　（송림동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877660</t>
+          <t xml:space="preserve">0877738</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4006,32 +4006,32 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">이천금고　장호원지점　　　　　</t>
+          <t xml:space="preserve">팔달금고　세화지점　　　　　　</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  641  3140 </t>
+          <t xml:space="preserve">031  236  9970 </t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  642  3141 </t>
+          <t xml:space="preserve">031  236  2106 </t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">17418 </t>
+          <t xml:space="preserve">16587 </t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260608</t>
+          <t xml:space="preserve">20260617</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　이천시　장호원읍　장감로　８１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　수원시　권선구　정조로　５３７　（세류동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -4048,7 +4048,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877673</t>
+          <t xml:space="preserve">0877741</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4058,32 +4058,32 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">이천금고　신하지점　　　　　　</t>
+          <t xml:space="preserve">팔달금고　권선지점　　　　　　</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  634  3774 </t>
+          <t xml:space="preserve">031  236  9975 </t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  634  3776 </t>
+          <t xml:space="preserve">031  234  7981 </t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">17327 </t>
+          <t xml:space="preserve">16589 </t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260608</t>
+          <t xml:space="preserve">20260617</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　이천시　부발읍　경충대로　２２３６　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　수원시　권선구　세지로２８번길　４２　（세류동）　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -4095,47 +4095,47 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877686</t>
+          <t xml:space="preserve">0701228</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">수협중앙회　　　　　</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">이천금고　마장지점　　　　　　</t>
+          <t xml:space="preserve">거제수협　외대역금융센터　　　</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  633  3140 </t>
+          <t xml:space="preserve">02   962  2280 </t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  631  3141 </t>
+          <t xml:space="preserve">02   962  2282 </t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">17387 </t>
+          <t xml:space="preserve">02418 </t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260608</t>
+          <t xml:space="preserve">20260616</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　이천시　마장면　오천로　５１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　동대문구　이문로　１２０　（이문동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4152,42 +4152,42 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">0233000</t>
+          <t xml:space="preserve">0802525</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＳＣ제일　　　　　　</t>
+          <t xml:space="preserve">하나　　　　　　　　</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">홍대입구역　　　　　　　　　　</t>
+          <t xml:space="preserve">골드클럽　올림픽선수촌ＰＢ센터</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   334  0123 </t>
+          <t xml:space="preserve">02   406  6672 </t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   334  0047 </t>
+          <t xml:space="preserve">02   400  4069 </t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">04056 </t>
+          <t xml:space="preserve">05648 </t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260605</t>
+          <t xml:space="preserve">20260615</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　마포구　신촌로　１２　２층　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울　송파구　양재대로　１２２２　（방이동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4204,42 +4204,42 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">0234805</t>
+          <t xml:space="preserve">0811639</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＳＣ제일　　　　　　</t>
+          <t xml:space="preserve">하나　　　　　　　　</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">송도국제도시　　　　　　　　　</t>
+          <t xml:space="preserve">화곡역금융센터　　　　　　　　</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">032  834  3535 </t>
+          <t xml:space="preserve">02   2693 1111 </t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">032  834  3883 </t>
+          <t xml:space="preserve">02   2607 0830 </t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">406840</t>
+          <t xml:space="preserve">157922</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260605</t>
+          <t xml:space="preserve">20260615</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">인천　연수구　송도동　３－２５　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울　강서구　화곡３동　１０５１－１７번지　대사빌딩　１층　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4251,47 +4251,47 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877657</t>
+          <t xml:space="preserve">0812366</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">하나　　　　　　　　</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">금강금고　사비지점　　　　　　</t>
+          <t xml:space="preserve">골드클럽　아시아선수촌ＰＢ센터</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">041  408  8282 </t>
+          <t xml:space="preserve">02   472  1111 </t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">041  408  8283 </t>
+          <t xml:space="preserve">02   420  2322 </t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">33158 </t>
+          <t xml:space="preserve">138797</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260605</t>
+          <t xml:space="preserve">20260615</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">충청남도　부여군　부여읍　성왕로　３５０－１　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울　송파구　잠실７동　８５－１　아시아선수촌상가１층　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -4308,42 +4308,42 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t xml:space="preserve">0133414</t>
+          <t xml:space="preserve">0812816</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">하나　　　　　　　　</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">입면농협　　　　　　　　　　　</t>
+          <t xml:space="preserve">왕십리금융센터　　　　　　　　</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  362  6005 </t>
+          <t xml:space="preserve">02   2294 1111 </t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">0503 8880 3927 </t>
+          <t xml:space="preserve">02   2297 7181 </t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">57513 </t>
+          <t xml:space="preserve">133030</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260604</t>
+          <t xml:space="preserve">20260615</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">전라남도　곡성군　입면　입면로　６８３　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울시　성동구　홍익동　１２５　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -4360,42 +4360,42 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">0143640</t>
+          <t xml:space="preserve">0819204</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">하나　　　　　　　　</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">제천　역전　　　　　　　　　　</t>
+          <t xml:space="preserve">골드클럽　영업１부　ＰＢ센터　</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  643  3769 </t>
+          <t xml:space="preserve">02   737  1111 </t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  646  3769 </t>
+          <t xml:space="preserve">02   757  6692 </t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">27196 </t>
+          <t xml:space="preserve">04523 </t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260604</t>
+          <t xml:space="preserve">20260615</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">충청북도　제천시　내토로　４４２　（화산동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　중구　을지로　３５（을지로１가）　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -4407,12 +4407,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">0452056</t>
+          <t xml:space="preserve">0877699</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4422,32 +4422,32 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">마포역　　　　　　　　　　　　</t>
+          <t xml:space="preserve">동군산금고　양안금고　　　　　</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   713  0324 </t>
+          <t xml:space="preserve">063  471  2442 </t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   703  7846 </t>
+          <t xml:space="preserve">063  451  4777 </t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">04172 </t>
+          <t xml:space="preserve">54074 </t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260604</t>
+          <t xml:space="preserve">20260615</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　마포구　도화길　１４　（도화동）　２층　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전북특별자치도　군산시　부골１길　４７　（조촌동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -4459,12 +4459,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve">0453505</t>
+          <t xml:space="preserve">0877709</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4474,32 +4474,32 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">신신　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">동군산금고　발산지점　　　　　</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   869  2173 </t>
+          <t xml:space="preserve">063  451  4334 </t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   869  2175 </t>
+          <t xml:space="preserve">063  451  4774 </t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">08774 </t>
+          <t xml:space="preserve">54065 </t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260604</t>
+          <t xml:space="preserve">20260615</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　관악구　신원로　１５　（신림동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전북특별자치도　군산시　개정면　바르메길　３９　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -4516,42 +4516,42 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t xml:space="preserve">0866040</t>
+          <t xml:space="preserve">2708504</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">하나증권　　　　　　</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">수성１가금고제１지점　　　　　</t>
+          <t xml:space="preserve">전주　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  763  0165 </t>
+          <t xml:space="preserve">063  276  1212 </t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  756  9717 </t>
+          <t xml:space="preserve">063  253  2033 </t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">42130 </t>
+          <t xml:space="preserve">54966 </t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260604</t>
+          <t xml:space="preserve">20260615</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">대구광역시　수성구　명덕로７６길　６４　（수성동１가）　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전북특별자치도　전주시　완산구　홍산로　２６１　（효자동２가），　ＢＹＣ건물　１층　　　　　　　　　</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -4568,42 +4568,42 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2090830</t>
+          <t xml:space="preserve">0459473</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">유안타증권　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">매직국민　　　　　　　　　　　</t>
+          <t xml:space="preserve">나주동부　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3770 2000 </t>
+          <t xml:space="preserve">061  331  1557 </t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   335  7332 </t>
+          <t xml:space="preserve">061  331  5547 </t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">07339 </t>
+          <t xml:space="preserve">58227 </t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260604</t>
+          <t xml:space="preserve">20260612</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전라남도　나주시　남평읍　강변１길　７３－１２　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -4620,42 +4620,42 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2090869</t>
+          <t xml:space="preserve">0874786</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">유안타증권　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">매직씨티　　　　　　　　　　　</t>
+          <t xml:space="preserve">소양강금고약사지점　　　　　　</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3770 2000 </t>
+          <t xml:space="preserve">033  252  7559 </t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   335  7332 </t>
+          <t xml:space="preserve">033  252  7550 </t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">07339 </t>
+          <t xml:space="preserve">24357 </t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260604</t>
+          <t xml:space="preserve">20260612</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">강원특별자치도　춘천시　공지로　４００　－１００５　１층　１０６호　소양강금고　약사지점　　　　　　</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -4672,42 +4672,42 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2090885</t>
+          <t xml:space="preserve">0875235</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">유안타증권　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">매직우리　　　　　　　　　　　</t>
+          <t xml:space="preserve">나주동부금고남평지점　　　　　</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3770 2000 </t>
+          <t xml:space="preserve">061  336  1557 </t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   335  7332 </t>
+          <t xml:space="preserve">061  336  5547 </t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">07339 </t>
+          <t xml:space="preserve">58227 </t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260604</t>
+          <t xml:space="preserve">20260612</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전라남도　나주시　남평읍　남평２로　４１－５　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -4719,47 +4719,47 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2090908</t>
+          <t xml:space="preserve">0805810</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">유안타증권　　　　　</t>
+          <t xml:space="preserve">하나　　　　　　　　</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">매직신한　　　　　　　　　　　</t>
+          <t xml:space="preserve">검단구청　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3770 2000 </t>
+          <t xml:space="preserve">032  766  1111 </t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   335  7332 </t>
+          <t xml:space="preserve">032  262  1092 </t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">07339 </t>
+          <t xml:space="preserve">22679 </t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260604</t>
+          <t xml:space="preserve">20260611</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">인천광역시　서구　독정로１２５번길　１２　（당하동）　당하동　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -4776,42 +4776,42 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2090940</t>
+          <t xml:space="preserve">0121015</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">유안타증권　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">매직기업　　　　　　　　　　　</t>
+          <t xml:space="preserve">금왕농협　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3770 2000 </t>
+          <t xml:space="preserve">043  877  0841 </t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   335  7332 </t>
+          <t xml:space="preserve">0503 8880 2300 </t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">07339 </t>
+          <t xml:space="preserve">27629 </t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260604</t>
+          <t xml:space="preserve">20260610</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">충청북도　음성군　금왕읍　무극로　２９３　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -4828,42 +4828,42 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2090953</t>
+          <t xml:space="preserve">0144005</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">유안타증권　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">매직농협　　　　　　　　　　　</t>
+          <t xml:space="preserve">동부　낙서　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3770 2000 </t>
+          <t xml:space="preserve">055  572  7018 </t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   335  7332 </t>
+          <t xml:space="preserve">0503 8880 5630 </t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">07339 </t>
+          <t xml:space="preserve">52108 </t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260604</t>
+          <t xml:space="preserve">20260610</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　의령군　낙서면　낙서로　５２３　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -4880,42 +4880,42 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091046</t>
+          <t xml:space="preserve">0150691</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve">유안타증권　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">매직하나　　　　　　　　　　　</t>
+          <t xml:space="preserve">탕정　동산　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3770 2000 </t>
+          <t xml:space="preserve">041  534  1811 </t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   335  7332 </t>
+          <t xml:space="preserve">041  534  1904 </t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">07339 </t>
+          <t xml:space="preserve">31458 </t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260604</t>
+          <t xml:space="preserve">20260610</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">충청남도　아산시　탕정면　삼성로　４４０　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -4932,42 +4932,42 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091211</t>
+          <t xml:space="preserve">0850739</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">유안타증권　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">매직부산　　　　　　　　　　　</t>
+          <t xml:space="preserve">광양시금고마동지점　　　　　　</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3770 2000 </t>
+          <t xml:space="preserve">061  797  1490 </t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   335  7332 </t>
+          <t xml:space="preserve">061  795  8776 </t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">07339 </t>
+          <t xml:space="preserve">57778 </t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260604</t>
+          <t xml:space="preserve">20260610</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전남　광양시　진등길　５５－５　송보５차상가내　５１０－２０２　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -4984,42 +4984,42 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2092579</t>
+          <t xml:space="preserve">0043562</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">유안타증권　　　　　</t>
+          <t xml:space="preserve">ＫＢ국민　　　　　　</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">매직생명　　　　　　　　　　　</t>
+          <t xml:space="preserve">휘경동　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3770 2000 </t>
+          <t xml:space="preserve">02   2215 0963 </t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   335  7332 </t>
+          <t xml:space="preserve">02   2215 5040 </t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">07339 </t>
+          <t xml:space="preserve">02418 </t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260604</t>
+          <t xml:space="preserve">20260608</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　동대문구　이문로　１２０　（이문동），４１２－１번지　２층　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -5036,42 +5036,42 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2092595</t>
+          <t xml:space="preserve">0105109</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">유안타증권　　　　　</t>
+          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">제휴사업팀　ＡＴＭ　　　　　　</t>
+          <t xml:space="preserve">북의왕　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3770 2000 </t>
+          <t xml:space="preserve">031  425  0432 </t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3770 2599 </t>
+          <t xml:space="preserve">031  425  0430 </t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">07339 </t>
+          <t xml:space="preserve">16024 </t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260604</t>
+          <t xml:space="preserve">20260608</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　의왕시　포일로　２０　（내손동）　래미안에버하임아파트　１층　상가　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -5088,42 +5088,42 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2092650</t>
+          <t xml:space="preserve">0153818</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">유안타증권　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">고객지원팀　ＶＡＮ　　　　　　</t>
+          <t xml:space="preserve">태안　영통동　　　　　　　　　</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3770 2000 </t>
+          <t xml:space="preserve">031  204  3891 </t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3770 2599 </t>
+          <t xml:space="preserve">031  204  3895 </t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">07339 </t>
+          <t xml:space="preserve">16701 </t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260604</t>
+          <t xml:space="preserve">20260608</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　수원시　영통구　매영로　３６８　（영통동，　살구골현대아파트상가）　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -5140,42 +5140,42 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2092731</t>
+          <t xml:space="preserve">0804031</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">유안타증권　　　　　</t>
+          <t xml:space="preserve">하나　　　　　　　　</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">매직새마을금고　　　　　　　　</t>
+          <t xml:space="preserve">골드클럽　강남파이낸스ＰＢ센터</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   1588 2600 </t>
+          <t xml:space="preserve">02   554  3076 </t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   335  7332 </t>
+          <t xml:space="preserve">02   562  5509 </t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">07339 </t>
+          <t xml:space="preserve">06236 </t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260604</t>
+          <t xml:space="preserve">20260608</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울　강남구　테헤란로　１５２　（역삼동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -5192,27 +5192,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2092757</t>
+          <t xml:space="preserve">0805690</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">유안타증권　　　　　</t>
+          <t xml:space="preserve">하나　　　　　　　　</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">매직ＳＣ　　　　　　　　　　　</t>
+          <t xml:space="preserve">골드클럽　여의도ＰＢ센터　　　</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   1588 2600 </t>
+          <t xml:space="preserve">02   765  1111 </t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   335  7332 </t>
+          <t xml:space="preserve">02   784  8128 </t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -5222,12 +5222,12 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260604</t>
+          <t xml:space="preserve">20260608</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　브라이튼여의도　２층　　　</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -5244,42 +5244,42 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2092809</t>
+          <t xml:space="preserve">0811451</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">유안타증권　　　　　</t>
+          <t xml:space="preserve">하나　　　　　　　　</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ｏｐｅｒａｔｉｏｎ센터점　　　</t>
+          <t xml:space="preserve">골드클럽　평창동ＰＢ센터　　　</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3770 5520 </t>
+          <t xml:space="preserve">02   391  1111 </t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3770 5611 </t>
+          <t xml:space="preserve">02   395  8047 </t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">07339 </t>
+          <t xml:space="preserve">03009 </t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260604</t>
+          <t xml:space="preserve">20260608</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）３２층　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　종로구　평창문화로　８７　창진파크팰리스　１층　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -5296,42 +5296,42 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2092812</t>
+          <t xml:space="preserve">0814173</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">유안타증권　　　　　</t>
+          <t xml:space="preserve">하나　　　　　　　　</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">스마트센터　　　　　　　　　　</t>
+          <t xml:space="preserve">골드클럽　분당ＰＢ센터　　　　</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2012 8000 </t>
+          <t xml:space="preserve">031  779  1111 </t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3770 2548 </t>
+          <t xml:space="preserve">031  779  1222 </t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">07339 </t>
+          <t xml:space="preserve">463050</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260604</t>
+          <t xml:space="preserve">20260608</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　성남시　분당구　서현동　２６５－２번지　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -5348,42 +5348,42 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2092825</t>
+          <t xml:space="preserve">0815732</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">유안타증권　　　　　</t>
+          <t xml:space="preserve">하나　　　　　　　　</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">매직우체국금융　　　　　　　　</t>
+          <t xml:space="preserve">골드클럽　용산ＰＢ센터　　　　</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   1588 2600 </t>
+          <t xml:space="preserve">02   797  1111 </t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2634 7866 </t>
+          <t xml:space="preserve">02   797  8795 </t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">07339 </t>
+          <t xml:space="preserve">140240</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260604</t>
+          <t xml:space="preserve">20260608</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울시　용산구　서빙고동　２７１－１０６외　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -5400,42 +5400,42 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2092838</t>
+          <t xml:space="preserve">0819178</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">유안타증권　　　　　</t>
+          <t xml:space="preserve">하나　　　　　　　　</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">매직경남　　　　　　　　　　　</t>
+          <t xml:space="preserve">골드클럽　압구정ＰＢ센터　　　</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   1588 2600 </t>
+          <t xml:space="preserve">02   512  1111 </t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3770 2548 </t>
+          <t xml:space="preserve">02   542  9872 </t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">07339 </t>
+          <t xml:space="preserve">135894</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260604</t>
+          <t xml:space="preserve">20260608</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울　강남구　신사동　６１８－３　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -5447,47 +5447,47 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2095039</t>
+          <t xml:space="preserve">0877660</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">유안타증권　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">매직동양　　　　　　　　　　　</t>
+          <t xml:space="preserve">이천금고　장호원지점　　　　　</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3770 2000 </t>
+          <t xml:space="preserve">031  641  3140 </t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3770 2000 </t>
+          <t xml:space="preserve">031  642  3141 </t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">07339 </t>
+          <t xml:space="preserve">17418 </t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260604</t>
+          <t xml:space="preserve">20260608</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　이천시　장호원읍　장감로　８１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -5499,47 +5499,47 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2096009</t>
+          <t xml:space="preserve">0877673</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">유안타증권　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">신탁운용지점　　　　　　　　　</t>
+          <t xml:space="preserve">이천금고　신하지점　　　　　　</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3770 2000 </t>
+          <t xml:space="preserve">031  634  3774 </t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3770 7332 </t>
+          <t xml:space="preserve">031  634  3776 </t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">07339 </t>
+          <t xml:space="preserve">17327 </t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260604</t>
+          <t xml:space="preserve">20260608</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　유안타증권　　　　　　　　</t>
+          <t xml:space="preserve">경기도　이천시　부발읍　경충대로　２２３６　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -5551,47 +5551,47 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2099543</t>
+          <t xml:space="preserve">0877686</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">유안타증권　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">고객지원팀　　　　　　　　　　</t>
+          <t xml:space="preserve">이천금고　마장지점　　　　　　</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3770 5605 </t>
+          <t xml:space="preserve">031  633  3140 </t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3770 2566 </t>
+          <t xml:space="preserve">031  631  3141 </t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">07339 </t>
+          <t xml:space="preserve">17387 </t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260604</t>
+          <t xml:space="preserve">20260608</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　이천시　마장면　오천로　５１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -5608,42 +5608,42 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t xml:space="preserve">0143640</t>
+          <t xml:space="preserve">0233000</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">ＳＣ제일　　　　　　</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">제천　역전　　　　　　　　　　</t>
+          <t xml:space="preserve">홍대입구역　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  643  3769 </t>
+          <t xml:space="preserve">02   334  0123 </t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  646  3769 </t>
+          <t xml:space="preserve">02   334  0047 </t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">27185 </t>
+          <t xml:space="preserve">04056 </t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260602</t>
+          <t xml:space="preserve">20260605</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">충청북도　제천시　내토로　４２１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　마포구　신촌로　１２　２층　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -5660,42 +5660,42 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t xml:space="preserve">0020242</t>
+          <t xml:space="preserve">0234805</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">산업　　　　　　　　</t>
+          <t xml:space="preserve">ＳＣ제일　　　　　　</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">국민성장펀드　첨단산업전략기금</t>
+          <t xml:space="preserve">송도국제도시　　　　　　　　　</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   787  4000 </t>
+          <t xml:space="preserve">032  834  3535 </t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   787  5091 </t>
+          <t xml:space="preserve">032  834  3883 </t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">07242 </t>
+          <t xml:space="preserve">406840</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260601</t>
+          <t xml:space="preserve">20260605</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　영등포구　은행로　１４　（여의도동）　한국산업은행　본점　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">인천　연수구　송도동　３－２５　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -5707,47 +5707,47 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t xml:space="preserve">0039521</t>
+          <t xml:space="preserve">0877657</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">기업　　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">반월기업금융센터　　　　　　　</t>
+          <t xml:space="preserve">금강금고　사비지점　　　　　　</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  412  0740 </t>
+          <t xml:space="preserve">041  408  8282 </t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 075  0952 </t>
+          <t xml:space="preserve">041  408  8283 </t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">15433 </t>
+          <t xml:space="preserve">33158 </t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260601</t>
+          <t xml:space="preserve">20260605</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　안산시　단원구　동산로　６３　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">충청남도　부여군　부여읍　성왕로　３５０－１　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -5764,7 +5764,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t xml:space="preserve">0135810</t>
+          <t xml:space="preserve">0133414</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -5774,32 +5774,32 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">서포농협　　　　　　　　　　　</t>
+          <t xml:space="preserve">입면농협　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  853  1500 </t>
+          <t xml:space="preserve">061  362  6005 </t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  853  1506 </t>
+          <t xml:space="preserve">0503 8880 3927 </t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">52543 </t>
+          <t xml:space="preserve">57513 </t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260601</t>
+          <t xml:space="preserve">20260604</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　사천시　서포면　사천대교로　７２１　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전라남도　곡성군　입면　입면로　６８３　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -5816,42 +5816,42 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t xml:space="preserve">0198983</t>
+          <t xml:space="preserve">0143640</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＫＢ국민　　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">전북혁신도시（점）　　　　　　</t>
+          <t xml:space="preserve">제천　역전　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">000  0000 0000 </t>
+          <t xml:space="preserve">043  643  3769 </t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">000  0000 0000 </t>
+          <t xml:space="preserve">043  646  3769 </t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">54871 </t>
+          <t xml:space="preserve">27196 </t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260601</t>
+          <t xml:space="preserve">20260604</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">전북특별자치도　전주시　덕진구　안전로　１４４　（중동）　１층　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">충청북도　제천시　내토로　４４２　（화산동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -5863,52 +5863,52 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t xml:space="preserve">0507370</t>
+          <t xml:space="preserve">0452056</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">저축은행　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">제이티친애　잠실（지）　　　　</t>
+          <t xml:space="preserve">마포역　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2240 6300 </t>
+          <t xml:space="preserve">02   713  0324 </t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   416  0094 </t>
+          <t xml:space="preserve">02   703  7846 </t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">05502 </t>
+          <t xml:space="preserve">04172 </t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260601</t>
+          <t xml:space="preserve">20260604</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　송파구　올림픽로　１４５，　리센츠상가　４층　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　마포구　도화길　１４　（도화동）　２층　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t xml:space="preserve">0507312</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
@@ -5920,42 +5920,42 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t xml:space="preserve">0802130</t>
+          <t xml:space="preserve">0453505</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나　　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">구로기업센터　　　　　　　　　</t>
+          <t xml:space="preserve">신신　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   864  5554 </t>
+          <t xml:space="preserve">02   869  2173 </t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   868  3390 </t>
+          <t xml:space="preserve">02   869  2175 </t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">08316 </t>
+          <t xml:space="preserve">08774 </t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260601</t>
+          <t xml:space="preserve">20260604</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　구로구　구로동로　１１５　（구로동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　관악구　신원로　１５　（신림동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -5972,42 +5972,42 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t xml:space="preserve">0802813</t>
+          <t xml:space="preserve">0866040</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나　　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">양재금융센터　　　　　　　　　</t>
+          <t xml:space="preserve">수성１가금고제１지점　　　　　</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   571  6149 </t>
+          <t xml:space="preserve">053  763  0165 </t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   578  3467 </t>
+          <t xml:space="preserve">053  756  9717 </t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">06752 </t>
+          <t xml:space="preserve">42130 </t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260601</t>
+          <t xml:space="preserve">20260604</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울　서초구　강남대로２７길　７－１５　（양재동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">대구광역시　수성구　명덕로７６길　６４　（수성동１가）　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -6024,42 +6024,42 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t xml:space="preserve">0804154</t>
+          <t xml:space="preserve">2090830</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나　　　　　　　　</t>
+          <t xml:space="preserve">유안타증권　　　　　</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">공덕동금융센터　　　　　　　　</t>
+          <t xml:space="preserve">매직국민　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   715  1372 </t>
+          <t xml:space="preserve">02   3770 2000 </t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   715  1528 </t>
+          <t xml:space="preserve">02   335  7332 </t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">04143 </t>
+          <t xml:space="preserve">07339 </t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260601</t>
+          <t xml:space="preserve">20260604</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울　마포구　마포대로　１３７　（공덕동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -6076,42 +6076,42 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t xml:space="preserve">0812612</t>
+          <t xml:space="preserve">2090869</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나　　　　　　　　</t>
+          <t xml:space="preserve">유안타증권　　　　　</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">공덕역금융센터　　　　　　　　</t>
+          <t xml:space="preserve">매직씨티　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   706  1111 </t>
+          <t xml:space="preserve">02   3770 2000 </t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   706  4981 </t>
+          <t xml:space="preserve">02   335  7332 </t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">121710</t>
+          <t xml:space="preserve">07339 </t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260601</t>
+          <t xml:space="preserve">20260604</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울　마포구　공덕동　２５４－８　별정우체국연합빌딩　１층　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -6128,42 +6128,42 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t xml:space="preserve">0863726</t>
+          <t xml:space="preserve">2090885</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">유안타증권　　　　　</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">김해시민금고진영１지점　　　　</t>
+          <t xml:space="preserve">매직우리　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  343  9700 </t>
+          <t xml:space="preserve">02   3770 2000 </t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  343  9705 </t>
+          <t xml:space="preserve">02   335  7332 </t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">50865 </t>
+          <t xml:space="preserve">07339 </t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260601</t>
+          <t xml:space="preserve">20260604</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　김해시　진영읍　여래로　２２　김해시민새마을금고　진영지점　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -6180,42 +6180,42 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2180892</t>
+          <t xml:space="preserve">2090908</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＫＢ증권　　　　　　</t>
+          <t xml:space="preserve">유안타증권　　　　　</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">전북혁신도시라운지　　　　　　</t>
+          <t xml:space="preserve">매직신한　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  916  7400 </t>
+          <t xml:space="preserve">02   3770 2000 </t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  916  7499 </t>
+          <t xml:space="preserve">02   335  7332 </t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">54871 </t>
+          <t xml:space="preserve">07339 </t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260601</t>
+          <t xml:space="preserve">20260604</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">전북특별자치도　전주시　덕진구　안전로　１４４　，　１층　（중동，엔씨빌딩）　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -6232,42 +6232,42 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2701103</t>
+          <t xml:space="preserve">2090940</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나증권　　　　　　</t>
+          <t xml:space="preserve">유안타증권　　　　　</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＴＨＥ　Ｈ１　Ｗ　　　　　　　</t>
+          <t xml:space="preserve">매직기업　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2694 5282 </t>
+          <t xml:space="preserve">02   3770 2000 </t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2694 5715 </t>
+          <t xml:space="preserve">02   335  7332 </t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">07998 </t>
+          <t xml:space="preserve">07339 </t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260601</t>
+          <t xml:space="preserve">20260604</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　양천구　목동동로　２５７　（목동，　현대하이페리온），　６층　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -6279,47 +6279,47 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t xml:space="preserve">0185307</t>
+          <t xml:space="preserve">2090953</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">유안타증권　　　　　</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">　광혜원　화랑　　　　　　　　</t>
+          <t xml:space="preserve">매직농협　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  000  0000 </t>
+          <t xml:space="preserve">02   3770 2000 </t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  000  0000 </t>
+          <t xml:space="preserve">02   335  7332 </t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">27805 </t>
+          <t xml:space="preserve">07339 </t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260529</t>
+          <t xml:space="preserve">20260604</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">충청북도　진천군　광혜원면　장기길　９１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -6336,42 +6336,42 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t xml:space="preserve">0454601</t>
+          <t xml:space="preserve">2091046</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">유안타증권　　　　　</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">부산동구　　　　　　　　　　　</t>
+          <t xml:space="preserve">매직하나　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">051  633  5743 </t>
+          <t xml:space="preserve">02   3770 2000 </t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">051  633  5752 </t>
+          <t xml:space="preserve">02   335  7332 </t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">48735 </t>
+          <t xml:space="preserve">07339 </t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260528</t>
+          <t xml:space="preserve">20260604</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">부산광역시　동구　범일로　１０１－８　（범일동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -6388,42 +6388,42 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t xml:space="preserve">0874016</t>
+          <t xml:space="preserve">2091211</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">유안타증권　　　　　</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">애플금고　칠금지점　　　　　　</t>
+          <t xml:space="preserve">매직부산　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  845  4501 </t>
+          <t xml:space="preserve">02   3770 2000 </t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  845  4503 </t>
+          <t xml:space="preserve">02   335  7332 </t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">27354 </t>
+          <t xml:space="preserve">07339 </t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260528</t>
+          <t xml:space="preserve">20260604</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">충청북도　충주시　번영대로　１６　（칠금동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -6440,42 +6440,42 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t xml:space="preserve">0143064</t>
+          <t xml:space="preserve">2092579</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">유안타증권　　　　　</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">송산　사강　　　　　　　　　　</t>
+          <t xml:space="preserve">매직생명　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  357  6800 </t>
+          <t xml:space="preserve">02   3770 2000 </t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  357  6880 </t>
+          <t xml:space="preserve">02   335  7332 </t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">18550 </t>
+          <t xml:space="preserve">07339 </t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260527</t>
+          <t xml:space="preserve">20260604</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　화성시　만세구　송산면　사강로　１８８　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -6492,42 +6492,42 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t xml:space="preserve">0143077</t>
+          <t xml:space="preserve">2092595</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">유안타증권　　　　　</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">태안　안녕　　　　　　　　　　</t>
+          <t xml:space="preserve">제휴사업팀　ＡＴＭ　　　　　　</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  236  3301 </t>
+          <t xml:space="preserve">02   3770 2000 </t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  236  3002 </t>
+          <t xml:space="preserve">02   3770 2599 </t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">18362 </t>
+          <t xml:space="preserve">07339 </t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260527</t>
+          <t xml:space="preserve">20260604</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　화성시　병점구　용주로　２２　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -6544,42 +6544,42 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t xml:space="preserve">0146281</t>
+          <t xml:space="preserve">2092650</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">유안타증권　　　　　</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">한국화훼농협　　　　　　　　　</t>
+          <t xml:space="preserve">고객지원팀　ＶＡＮ　　　　　　</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  910  8001 </t>
+          <t xml:space="preserve">02   3770 2000 </t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  910  8010 </t>
+          <t xml:space="preserve">02   3770 2599 </t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">10226 </t>
+          <t xml:space="preserve">07339 </t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260527</t>
+          <t xml:space="preserve">20260604</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　고양시　일산서구　대화로　３６２　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -6596,42 +6596,42 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t xml:space="preserve">0155227</t>
+          <t xml:space="preserve">2092731</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">유안타증권　　　　　</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">태안　중앙　　　　　　　　　　</t>
+          <t xml:space="preserve">매직새마을금고　　　　　　　　</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  267  3894 </t>
+          <t xml:space="preserve">02   1588 2600 </t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  267  3898 </t>
+          <t xml:space="preserve">02   335  7332 </t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">18391 </t>
+          <t xml:space="preserve">07339 </t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260527</t>
+          <t xml:space="preserve">20260604</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　화성시　병점구　병점중앙로　１９５　２０１호（진안동，　창현빌딩）　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -6648,42 +6648,42 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t xml:space="preserve">0155256</t>
+          <t xml:space="preserve">2092757</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">유안타증권　　　　　</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">태안　기산　　　　　　　　　　</t>
+          <t xml:space="preserve">매직ＳＣ　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  221  3066 </t>
+          <t xml:space="preserve">02   1588 2600 </t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  221  3098 </t>
+          <t xml:space="preserve">02   335  7332 </t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">18385 </t>
+          <t xml:space="preserve">07339 </t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260527</t>
+          <t xml:space="preserve">20260604</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　화성시　병점구　효행로　１１６１　대림프라자　２０３호　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -6700,42 +6700,42 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t xml:space="preserve">0180865</t>
+          <t xml:space="preserve">2092809</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">유안타증권　　　　　</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">태안　서동탄역　　　　　　　　</t>
+          <t xml:space="preserve">Ｏｐｅｒａｔｉｏｎ센터점　　　</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  8015 2344 </t>
+          <t xml:space="preserve">02   3770 5520 </t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  8015 2349 </t>
+          <t xml:space="preserve">02   3770 5611 </t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">18429 </t>
+          <t xml:space="preserve">07339 </t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260527</t>
+          <t xml:space="preserve">20260604</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　화성시　동탄구　１０용사로　３４３－２　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）３２층　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -6752,42 +6752,42 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t xml:space="preserve">0182012</t>
+          <t xml:space="preserve">2092812</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">유안타증권　　　　　</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">태안농협　능동　　　　　　　　</t>
+          <t xml:space="preserve">스마트센터　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  234  1100 </t>
+          <t xml:space="preserve">02   2012 8000 </t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  237  9912 </t>
+          <t xml:space="preserve">02   3770 2548 </t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">18421 </t>
+          <t xml:space="preserve">07339 </t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260527</t>
+          <t xml:space="preserve">20260604</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　화성시　병점구　동탄지성로　１６６　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -6799,99 +6799,99 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t xml:space="preserve">0374820</t>
+          <t xml:space="preserve">2092825</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve">전북　　　　　　　　</t>
+          <t xml:space="preserve">유안타증권　　　　　</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">오토금융센터　　　　　　　　　</t>
+          <t xml:space="preserve">매직우체국금융　　　　　　　　</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   1522 0034 </t>
+          <t xml:space="preserve">02   1588 2600 </t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3145 4105 </t>
+          <t xml:space="preserve">02   2634 7866 </t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">04034 </t>
+          <t xml:space="preserve">07339 </t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260527</t>
+          <t xml:space="preserve">20260604</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　마포구　양화로　８５　동현빌딩　８층　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t xml:space="preserve">0374817</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t xml:space="preserve">0781442</t>
+          <t xml:space="preserve">2092838</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＫＢ국민　　　　　　</t>
+          <t xml:space="preserve">유안타증권　　　　　</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">고객컨택영업２전주　　　　　　</t>
+          <t xml:space="preserve">매직경남　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800 9999 0000 </t>
+          <t xml:space="preserve">02   1588 2600 </t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800 9999 0000 </t>
+          <t xml:space="preserve">02   3770 2548 </t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">54871 </t>
+          <t xml:space="preserve">07339 </t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260527</t>
+          <t xml:space="preserve">20260604</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">전북특별자치도　전주시　덕진구　안전로　１４４　（중동）　５층　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -6908,42 +6908,42 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t xml:space="preserve">0113874</t>
+          <t xml:space="preserve">2095039</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
+          <t xml:space="preserve">유안타증권　　　　　</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">작전동　　　　　　　　　　　　</t>
+          <t xml:space="preserve">매직동양　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">032  552  4121 </t>
+          <t xml:space="preserve">02   3770 2000 </t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">032  552  0437 </t>
+          <t xml:space="preserve">02   3770 2000 </t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">21120 </t>
+          <t xml:space="preserve">07339 </t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260526</t>
+          <t xml:space="preserve">20260604</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">인천광역시　계양구　계양대로　４４　（작전동），　덕용프라자　５０１호　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -6955,50 +6955,830 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
+          <t xml:space="preserve">변경    </t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2096009</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">유안타증권　　　　　</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신탁운용지점　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02   3770 2000 </t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02   3770 7332 </t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07339 </t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20260604</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　유안타증권　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       </t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">변경    </t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2099543</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">유안타증권　　　　　</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">고객지원팀　　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02   3770 5605 </t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02   3770 2566 </t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07339 </t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20260604</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서울특별시　영등포구　국제금융로　３９　（여의도동，　브라이튼　여의도）　　　　　　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       </t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">변경    </t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0143640</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">농축협　　　　　　　</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">제천　역전　　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">043  643  3769 </t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">043  646  3769 </t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27185 </t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20260602</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">충청북도　제천시　내토로　４２１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       </t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">변경    </t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0020242</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">산업　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">국민성장펀드　첨단산업전략기금</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02   787  4000 </t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02   787  5091 </t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07242 </t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20260601</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서울특별시　영등포구　은행로　１４　（여의도동）　한국산업은행　본점　　　　　　　　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       </t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">변경    </t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0039521</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기업　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">반월기업금융센터　　　　　　　</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">031  412  0740 </t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0505 075  0952 </t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15433 </t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20260601</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">경기도　안산시　단원구　동산로　６３　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       </t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">변경    </t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0135810</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">농축협　　　　　　　</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포농협　　　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">055  853  1500 </t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">055  853  1506 </t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52543 </t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20260601</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">경상남도　사천시　서포면　사천대교로　７２１　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       </t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">변경    </t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0198983</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ＫＢ국민　　　　　　</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전북혁신도시（점）　　　　　　</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000  0000 0000 </t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000  0000 0000 </t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54871 </t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20260601</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전북특별자치도　전주시　덕진구　안전로　１４４　（중동）　１층　　　　　　　　　　　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       </t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">폐쇄    </t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0507370</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">저축은행　　　　　　</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">제이티친애　잠실（지）　　　　</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02   2240 6300 </t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02   416  0094 </t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05502 </t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20260601</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서울특별시　송파구　올림픽로　１４５，　리센츠상가　４층　　　　　　　　　　　　　　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0507312</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">변경    </t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0802130</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">하나　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구로기업센터　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02   864  5554 </t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02   868  3390 </t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08316 </t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20260601</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서울특별시　구로구　구로동로　１１５　（구로동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       </t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">변경    </t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0802813</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">하나　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">양재금융센터　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02   571  6149 </t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02   578  3467 </t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06752 </t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20260601</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서울　서초구　강남대로２７길　７－１５　（양재동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       </t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">변경    </t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0804154</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">하나　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">공덕동금융센터　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02   715  1372 </t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02   715  1528 </t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04143 </t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20260601</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서울　마포구　마포대로　１３７　（공덕동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       </t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">변경    </t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0812612</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">하나　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">공덕역금융센터　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02   706  1111 </t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02   706  4981 </t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121710</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20260601</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서울　마포구　공덕동　２５４－８　별정우체국연합빌딩　１층　　　　　　　　　　　　　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       </t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">변경    </t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0863726</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">새마을금고　　　　　</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김해시민금고진영１지점　　　　</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">055  343  9700 </t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">055  343  9705 </t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50865 </t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20260601</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">경상남도　김해시　진영읍　여래로　２２　김해시민새마을금고　진영지점　　　　　　　　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       </t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">변경    </t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2180892</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ＫＢ증권　　　　　　</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전북혁신도시라운지　　　　　　</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">063  916  7400 </t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">063  916  7499 </t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54871 </t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20260601</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전북특별자치도　전주시　덕진구　안전로　１４４　，　１층　（중동，엔씨빌딩）　　　　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       </t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">변경    </t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2701103</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">하나증권　　　　　　</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ＴＨＥ　Ｈ１　Ｗ　　　　　　　</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02   2694 5282 </t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02   2694 5715 </t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07998 </t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20260601</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서울특별시　양천구　목동동로　２５７　（목동，　현대하이페리온），　６층　　　　　　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       </t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
           <t xml:space="preserve">신규    </t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0808406</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">하나　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">글로벌증권관리팀　　　　　　　</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02   729  0500 </t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02   2002 1465 </t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04538 </t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260526</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">서울특별시　중구　을지로　６６　（을지로２가）　하나금융그룹명동사옥　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
+      <c r="B149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0185307</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">농축협　　　　　　　</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　광혜원　화랑　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">043  000  0000 </t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">043  000  0000 </t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27805 </t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20260529</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">충청북도　진천군　광혜원면　장기길　９１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
         <is>
           <t xml:space="preserve">       </t>
         </is>

--- a/src/test/resources/codechgfile.text.xlsx
+++ b/src/test/resources/codechgfile.text.xlsx
@@ -34,7 +34,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J904"/>
+  <dimension ref="A1:J876"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -45588,1462 +45588,6 @@
         </is>
       </c>
     </row>
-    <row r="877">
-      <c r="A877" t="inlineStr">
-        <is>
-          <t xml:space="preserve">변경    </t>
-        </is>
-      </c>
-      <c r="B877" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0120702</t>
-        </is>
-      </c>
-      <c r="C877" t="inlineStr">
-        <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
-        </is>
-      </c>
-      <c r="D877" t="inlineStr">
-        <is>
-          <t xml:space="preserve">인천옹진농협　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="E877" t="inlineStr">
-        <is>
-          <t xml:space="preserve">032  885  2001 </t>
-        </is>
-      </c>
-      <c r="F877" t="inlineStr">
-        <is>
-          <t xml:space="preserve">032  885  2006 </t>
-        </is>
-      </c>
-      <c r="G877" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22331 </t>
-        </is>
-      </c>
-      <c r="H877" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260716</t>
-        </is>
-      </c>
-      <c r="I877" t="inlineStr">
-        <is>
-          <t xml:space="preserve">인천광역시　제물포구　인중로４１번길　１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J877" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="878">
-      <c r="A878" t="inlineStr">
-        <is>
-          <t xml:space="preserve">변경    </t>
-        </is>
-      </c>
-      <c r="B878" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0141516</t>
-        </is>
-      </c>
-      <c r="C878" t="inlineStr">
-        <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
-        </is>
-      </c>
-      <c r="D878" t="inlineStr">
-        <is>
-          <t xml:space="preserve">서인천　율도　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="E878" t="inlineStr">
-        <is>
-          <t xml:space="preserve">032  578  8256 </t>
-        </is>
-      </c>
-      <c r="F878" t="inlineStr">
-        <is>
-          <t xml:space="preserve">032  578  8140 </t>
-        </is>
-      </c>
-      <c r="G878" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22786 </t>
-        </is>
-      </c>
-      <c r="H878" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260716</t>
-        </is>
-      </c>
-      <c r="I878" t="inlineStr">
-        <is>
-          <t xml:space="preserve">인천광역시　서해구　율도로　３２　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J878" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="879">
-      <c r="A879" t="inlineStr">
-        <is>
-          <t xml:space="preserve">변경    </t>
-        </is>
-      </c>
-      <c r="B879" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0149589</t>
-        </is>
-      </c>
-      <c r="C879" t="inlineStr">
-        <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
-        </is>
-      </c>
-      <c r="D879" t="inlineStr">
-        <is>
-          <t xml:space="preserve">서인천　서곶　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="E879" t="inlineStr">
-        <is>
-          <t xml:space="preserve">032  561  9801 </t>
-        </is>
-      </c>
-      <c r="F879" t="inlineStr">
-        <is>
-          <t xml:space="preserve">032  561  9804 </t>
-        </is>
-      </c>
-      <c r="G879" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22724 </t>
-        </is>
-      </c>
-      <c r="H879" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260716</t>
-        </is>
-      </c>
-      <c r="I879" t="inlineStr">
-        <is>
-          <t xml:space="preserve">인천광역시　서해구　승학로　２５３　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J879" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="880">
-      <c r="A880" t="inlineStr">
-        <is>
-          <t xml:space="preserve">변경    </t>
-        </is>
-      </c>
-      <c r="B880" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0151881</t>
-        </is>
-      </c>
-      <c r="C880" t="inlineStr">
-        <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
-        </is>
-      </c>
-      <c r="D880" t="inlineStr">
-        <is>
-          <t xml:space="preserve">목포원예　신도심　　　　　　　</t>
-        </is>
-      </c>
-      <c r="E880" t="inlineStr">
-        <is>
-          <t xml:space="preserve">061  283  6321 </t>
-        </is>
-      </c>
-      <c r="F880" t="inlineStr">
-        <is>
-          <t xml:space="preserve">061  283  4777 </t>
-        </is>
-      </c>
-      <c r="G880" t="inlineStr">
-        <is>
-          <t xml:space="preserve">58696 </t>
-        </is>
-      </c>
-      <c r="H880" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260716</t>
-        </is>
-      </c>
-      <c r="I880" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전남광주통합특별시　목포시　교육로４１번길　２５　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J880" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="881">
-      <c r="A881" t="inlineStr">
-        <is>
-          <t xml:space="preserve">변경    </t>
-        </is>
-      </c>
-      <c r="B881" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0155395</t>
-        </is>
-      </c>
-      <c r="C881" t="inlineStr">
-        <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
-        </is>
-      </c>
-      <c r="D881" t="inlineStr">
-        <is>
-          <t xml:space="preserve">서인천　청라　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="E881" t="inlineStr">
-        <is>
-          <t xml:space="preserve">032  568  9320 </t>
-        </is>
-      </c>
-      <c r="F881" t="inlineStr">
-        <is>
-          <t xml:space="preserve">032  568  9321 </t>
-        </is>
-      </c>
-      <c r="G881" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22737 </t>
-        </is>
-      </c>
-      <c r="H881" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260716</t>
-        </is>
-      </c>
-      <c r="I881" t="inlineStr">
-        <is>
-          <t xml:space="preserve">인천광역시　서해구　중봉대로５８６번길　２２　청라엑슬루타워상가　Ｂ동２０６호　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J881" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="882">
-      <c r="A882" t="inlineStr">
-        <is>
-          <t xml:space="preserve">변경    </t>
-        </is>
-      </c>
-      <c r="B882" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0175346</t>
-        </is>
-      </c>
-      <c r="C882" t="inlineStr">
-        <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
-        </is>
-      </c>
-      <c r="D882" t="inlineStr">
-        <is>
-          <t xml:space="preserve">광주축산농협　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="E882" t="inlineStr">
-        <is>
-          <t xml:space="preserve">062  942  5885 </t>
-        </is>
-      </c>
-      <c r="F882" t="inlineStr">
-        <is>
-          <t xml:space="preserve">062  228  1080 </t>
-        </is>
-      </c>
-      <c r="G882" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62380 </t>
-        </is>
-      </c>
-      <c r="H882" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260716</t>
-        </is>
-      </c>
-      <c r="I882" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전남광주통합특별시　광산구　상무대로　３１３　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J882" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="883">
-      <c r="A883" t="inlineStr">
-        <is>
-          <t xml:space="preserve">변경    </t>
-        </is>
-      </c>
-      <c r="B883" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0175537</t>
-        </is>
-      </c>
-      <c r="C883" t="inlineStr">
-        <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
-        </is>
-      </c>
-      <c r="D883" t="inlineStr">
-        <is>
-          <t xml:space="preserve">순천광양　남부　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="E883" t="inlineStr">
-        <is>
-          <t xml:space="preserve">061  745  3700 </t>
-        </is>
-      </c>
-      <c r="F883" t="inlineStr">
-        <is>
-          <t xml:space="preserve">061  745  3747 </t>
-        </is>
-      </c>
-      <c r="G883" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57962 </t>
-        </is>
-      </c>
-      <c r="H883" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260716</t>
-        </is>
-      </c>
-      <c r="I883" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전남광주통합특별시　순천시　풍덕주택길　２６　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J883" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="884">
-      <c r="A884" t="inlineStr">
-        <is>
-          <t xml:space="preserve">잠정패쇄</t>
-        </is>
-      </c>
-      <c r="B884" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0184175</t>
-        </is>
-      </c>
-      <c r="C884" t="inlineStr">
-        <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
-        </is>
-      </c>
-      <c r="D884" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대전충남양계　두성　　　　　　</t>
-        </is>
-      </c>
-      <c r="E884" t="inlineStr">
-        <is>
-          <t xml:space="preserve">041  622  6305 </t>
-        </is>
-      </c>
-      <c r="F884" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0503 8880 2628 </t>
-        </is>
-      </c>
-      <c r="G884" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31112 </t>
-        </is>
-      </c>
-      <c r="H884" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260716</t>
-        </is>
-      </c>
-      <c r="I884" t="inlineStr">
-        <is>
-          <t xml:space="preserve">충청남도　천안시　서북구　두정공원２길　２６　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J884" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0173979</t>
-        </is>
-      </c>
-    </row>
-    <row r="885">
-      <c r="A885" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규    </t>
-        </is>
-      </c>
-      <c r="B885" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0508735</t>
-        </is>
-      </c>
-      <c r="C885" t="inlineStr">
-        <is>
-          <t xml:space="preserve">저축은행　　　　　　</t>
-        </is>
-      </c>
-      <c r="D885" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ＩＢＫ　　　종합금융４부　　　</t>
-        </is>
-      </c>
-      <c r="E885" t="inlineStr">
-        <is>
-          <t xml:space="preserve">051  791  4300 </t>
-        </is>
-      </c>
-      <c r="F885" t="inlineStr">
-        <is>
-          <t xml:space="preserve">051  791  4305 </t>
-        </is>
-      </c>
-      <c r="G885" t="inlineStr">
-        <is>
-          <t xml:space="preserve">47254 </t>
-        </is>
-      </c>
-      <c r="H885" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260716</t>
-        </is>
-      </c>
-      <c r="I885" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부산광역시　부산진구　중앙대로　７３５　（부전동）　３층　ＩＢＫ저축은행　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J885" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="886">
-      <c r="A886" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규    </t>
-        </is>
-      </c>
-      <c r="B886" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0023676</t>
-        </is>
-      </c>
-      <c r="C886" t="inlineStr">
-        <is>
-          <t xml:space="preserve">산업　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="D886" t="inlineStr">
-        <is>
-          <t xml:space="preserve">서남권투자금융센터　　　　　　</t>
-        </is>
-      </c>
-      <c r="E886" t="inlineStr">
-        <is>
-          <t xml:space="preserve">062  958  1057 </t>
-        </is>
-      </c>
-      <c r="F886" t="inlineStr">
-        <is>
-          <t xml:space="preserve">062  531  6038 </t>
-        </is>
-      </c>
-      <c r="G886" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62355 </t>
-        </is>
-      </c>
-      <c r="H886" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260715</t>
-        </is>
-      </c>
-      <c r="I886" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전남광주통합특별시　광산구　무진대로　２６１　（우산동）　５층　　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J886" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="887">
-      <c r="A887" t="inlineStr">
-        <is>
-          <t xml:space="preserve">변경    </t>
-        </is>
-      </c>
-      <c r="B887" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0102209</t>
-        </is>
-      </c>
-      <c r="C887" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
-        </is>
-      </c>
-      <c r="D887" t="inlineStr">
-        <is>
-          <t xml:space="preserve">송도금융센터　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="E887" t="inlineStr">
-        <is>
-          <t xml:space="preserve">032  858  0021 </t>
-        </is>
-      </c>
-      <c r="F887" t="inlineStr">
-        <is>
-          <t xml:space="preserve">032  858  0023 </t>
-        </is>
-      </c>
-      <c r="G887" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22013 </t>
-        </is>
-      </c>
-      <c r="H887" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260715</t>
-        </is>
-      </c>
-      <c r="I887" t="inlineStr">
-        <is>
-          <t xml:space="preserve">인천광역시　연수구　하모니로１７７번길　４９　（송도동）　　　　　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J887" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="888">
-      <c r="A888" t="inlineStr">
-        <is>
-          <t xml:space="preserve">변경    </t>
-        </is>
-      </c>
-      <c r="B888" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0466194</t>
-        </is>
-      </c>
-      <c r="C888" t="inlineStr">
-        <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
-        </is>
-      </c>
-      <c r="D888" t="inlineStr">
-        <is>
-          <t xml:space="preserve">김천대신　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="E888" t="inlineStr">
-        <is>
-          <t xml:space="preserve">054  433  5462 </t>
-        </is>
-      </c>
-      <c r="F888" t="inlineStr">
-        <is>
-          <t xml:space="preserve">054  437  5462 </t>
-        </is>
-      </c>
-      <c r="G888" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39548 </t>
-        </is>
-      </c>
-      <c r="H888" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260715</t>
-        </is>
-      </c>
-      <c r="I888" t="inlineStr">
-        <is>
-          <t xml:space="preserve">경북　김천시　부거리길　９　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J888" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="889">
-      <c r="A889" t="inlineStr">
-        <is>
-          <t xml:space="preserve">변경    </t>
-        </is>
-      </c>
-      <c r="B889" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0490351</t>
-        </is>
-      </c>
-      <c r="C889" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신협　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="D889" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부산장우신협　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="E889" t="inlineStr">
-        <is>
-          <t xml:space="preserve">051  464  0019 </t>
-        </is>
-      </c>
-      <c r="F889" t="inlineStr">
-        <is>
-          <t xml:space="preserve">051  464  0266 </t>
-        </is>
-      </c>
-      <c r="G889" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48814 </t>
-        </is>
-      </c>
-      <c r="H889" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260715</t>
-        </is>
-      </c>
-      <c r="I889" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부산광역시　동구　초량상로　９０－１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J889" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="890">
-      <c r="A890" t="inlineStr">
-        <is>
-          <t xml:space="preserve">변경    </t>
-        </is>
-      </c>
-      <c r="B890" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0877806</t>
-        </is>
-      </c>
-      <c r="C890" t="inlineStr">
-        <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
-        </is>
-      </c>
-      <c r="D890" t="inlineStr">
-        <is>
-          <t xml:space="preserve">김천대신금고　평화지점　　　　</t>
-        </is>
-      </c>
-      <c r="E890" t="inlineStr">
-        <is>
-          <t xml:space="preserve">054  434  1114 </t>
-        </is>
-      </c>
-      <c r="F890" t="inlineStr">
-        <is>
-          <t xml:space="preserve">054  435  5164 </t>
-        </is>
-      </c>
-      <c r="G890" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39609 </t>
-        </is>
-      </c>
-      <c r="H890" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260715</t>
-        </is>
-      </c>
-      <c r="I890" t="inlineStr">
-        <is>
-          <t xml:space="preserve">경상북도　김천시　김천로　１０６　（평화동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J890" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="891">
-      <c r="A891" t="inlineStr">
-        <is>
-          <t xml:space="preserve">변경    </t>
-        </is>
-      </c>
-      <c r="B891" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0124708</t>
-        </is>
-      </c>
-      <c r="C891" t="inlineStr">
-        <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
-        </is>
-      </c>
-      <c r="D891" t="inlineStr">
-        <is>
-          <t xml:space="preserve">보성농협　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="E891" t="inlineStr">
-        <is>
-          <t xml:space="preserve">061  850  7800 </t>
-        </is>
-      </c>
-      <c r="F891" t="inlineStr">
-        <is>
-          <t xml:space="preserve">061  853  6665 </t>
-        </is>
-      </c>
-      <c r="G891" t="inlineStr">
-        <is>
-          <t xml:space="preserve">59458 </t>
-        </is>
-      </c>
-      <c r="H891" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260714</t>
-        </is>
-      </c>
-      <c r="I891" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전남광주통합특별시　보성군　보성읍　현충로　９２－２０　　　　　　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J891" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="892">
-      <c r="A892" t="inlineStr">
-        <is>
-          <t xml:space="preserve">변경    </t>
-        </is>
-      </c>
-      <c r="B892" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0129871</t>
-        </is>
-      </c>
-      <c r="C892" t="inlineStr">
-        <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
-        </is>
-      </c>
-      <c r="D892" t="inlineStr">
-        <is>
-          <t xml:space="preserve">중구농협　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="E892" t="inlineStr">
-        <is>
-          <t xml:space="preserve">032  746  0989 </t>
-        </is>
-      </c>
-      <c r="F892" t="inlineStr">
-        <is>
-          <t xml:space="preserve">032  746  5078 </t>
-        </is>
-      </c>
-      <c r="G892" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23249 </t>
-        </is>
-      </c>
-      <c r="H892" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260714</t>
-        </is>
-      </c>
-      <c r="I892" t="inlineStr">
-        <is>
-          <t xml:space="preserve">인천광역시　영종구　운남로　１６６　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J892" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="893">
-      <c r="A893" t="inlineStr">
-        <is>
-          <t xml:space="preserve">변경    </t>
-        </is>
-      </c>
-      <c r="B893" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0134468</t>
-        </is>
-      </c>
-      <c r="C893" t="inlineStr">
-        <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
-        </is>
-      </c>
-      <c r="D893" t="inlineStr">
-        <is>
-          <t xml:space="preserve">서광주　화정　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="E893" t="inlineStr">
-        <is>
-          <t xml:space="preserve">062  372  0421 </t>
-        </is>
-      </c>
-      <c r="F893" t="inlineStr">
-        <is>
-          <t xml:space="preserve">062  373  0408 </t>
-        </is>
-      </c>
-      <c r="G893" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62026 </t>
-        </is>
-      </c>
-      <c r="H893" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260714</t>
-        </is>
-      </c>
-      <c r="I893" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전남광주통합특별시　서구　염화로　８１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J893" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="894">
-      <c r="A894" t="inlineStr">
-        <is>
-          <t xml:space="preserve">변경    </t>
-        </is>
-      </c>
-      <c r="B894" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0141794</t>
-        </is>
-      </c>
-      <c r="C894" t="inlineStr">
-        <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
-        </is>
-      </c>
-      <c r="D894" t="inlineStr">
-        <is>
-          <t xml:space="preserve">중구　용유　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="E894" t="inlineStr">
-        <is>
-          <t xml:space="preserve">032  746  3008 </t>
-        </is>
-      </c>
-      <c r="F894" t="inlineStr">
-        <is>
-          <t xml:space="preserve">032  746  9894 </t>
-        </is>
-      </c>
-      <c r="G894" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23360 </t>
-        </is>
-      </c>
-      <c r="H894" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260714</t>
-        </is>
-      </c>
-      <c r="I894" t="inlineStr">
-        <is>
-          <t xml:space="preserve">인천광역시　영종구　마시란로　３１４－１６　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J894" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="895">
-      <c r="A895" t="inlineStr">
-        <is>
-          <t xml:space="preserve">변경    </t>
-        </is>
-      </c>
-      <c r="B895" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0151153</t>
-        </is>
-      </c>
-      <c r="C895" t="inlineStr">
-        <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
-        </is>
-      </c>
-      <c r="D895" t="inlineStr">
-        <is>
-          <t xml:space="preserve">중구　하인천　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="E895" t="inlineStr">
-        <is>
-          <t xml:space="preserve">032  763  4602 </t>
-        </is>
-      </c>
-      <c r="F895" t="inlineStr">
-        <is>
-          <t xml:space="preserve">032  772  7353 </t>
-        </is>
-      </c>
-      <c r="G895" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22312 </t>
-        </is>
-      </c>
-      <c r="H895" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260714</t>
-        </is>
-      </c>
-      <c r="I895" t="inlineStr">
-        <is>
-          <t xml:space="preserve">인천광역시　제물포구　차이나타운로４４번길　３１－１３　　　　　　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J895" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="896">
-      <c r="A896" t="inlineStr">
-        <is>
-          <t xml:space="preserve">변경    </t>
-        </is>
-      </c>
-      <c r="B896" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0156323</t>
-        </is>
-      </c>
-      <c r="C896" t="inlineStr">
-        <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
-        </is>
-      </c>
-      <c r="D896" t="inlineStr">
-        <is>
-          <t xml:space="preserve">순천원예농협　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="E896" t="inlineStr">
-        <is>
-          <t xml:space="preserve">061  746  7500 </t>
-        </is>
-      </c>
-      <c r="F896" t="inlineStr">
-        <is>
-          <t xml:space="preserve">061  746  9530 </t>
-        </is>
-      </c>
-      <c r="G896" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57996 </t>
-        </is>
-      </c>
-      <c r="H896" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260714</t>
-        </is>
-      </c>
-      <c r="I896" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전남광주통합특별시　순천시　남산로　４６　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J896" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="897">
-      <c r="A897" t="inlineStr">
-        <is>
-          <t xml:space="preserve">변경    </t>
-        </is>
-      </c>
-      <c r="B897" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0159278</t>
-        </is>
-      </c>
-      <c r="C897" t="inlineStr">
-        <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
-        </is>
-      </c>
-      <c r="D897" t="inlineStr">
-        <is>
-          <t xml:space="preserve">중구　공항신도시　　　　　　　</t>
-        </is>
-      </c>
-      <c r="E897" t="inlineStr">
-        <is>
-          <t xml:space="preserve">032  752  1414 </t>
-        </is>
-      </c>
-      <c r="F897" t="inlineStr">
-        <is>
-          <t xml:space="preserve">032  752  1420 </t>
-        </is>
-      </c>
-      <c r="G897" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23211 </t>
-        </is>
-      </c>
-      <c r="H897" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260714</t>
-        </is>
-      </c>
-      <c r="I897" t="inlineStr">
-        <is>
-          <t xml:space="preserve">인천광역시　영종구　신도시남로１４２번길　６　（운서동）　　　　　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J897" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="898">
-      <c r="A898" t="inlineStr">
-        <is>
-          <t xml:space="preserve">변경    </t>
-        </is>
-      </c>
-      <c r="B898" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0180328</t>
-        </is>
-      </c>
-      <c r="C898" t="inlineStr">
-        <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
-        </is>
-      </c>
-      <c r="D898" t="inlineStr">
-        <is>
-          <t xml:space="preserve">중구　하늘도시　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="E898" t="inlineStr">
-        <is>
-          <t xml:space="preserve">032  746  1441 </t>
-        </is>
-      </c>
-      <c r="F898" t="inlineStr">
-        <is>
-          <t xml:space="preserve">032  746  1551 </t>
-        </is>
-      </c>
-      <c r="G898" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23303 </t>
-        </is>
-      </c>
-      <c r="H898" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260714</t>
-        </is>
-      </c>
-      <c r="I898" t="inlineStr">
-        <is>
-          <t xml:space="preserve">인천광역시　영종구　하늘중앙로１９５번길　１４　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J898" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="899">
-      <c r="A899" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규    </t>
-        </is>
-      </c>
-      <c r="B899" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0508670</t>
-        </is>
-      </c>
-      <c r="C899" t="inlineStr">
-        <is>
-          <t xml:space="preserve">저축은행　　　　　　</t>
-        </is>
-      </c>
-      <c r="D899" t="inlineStr">
-        <is>
-          <t xml:space="preserve">참　　　　　경영관리팀　　　　</t>
-        </is>
-      </c>
-      <c r="E899" t="inlineStr">
-        <is>
-          <t xml:space="preserve">053  720  7300 </t>
-        </is>
-      </c>
-      <c r="F899" t="inlineStr">
-        <is>
-          <t xml:space="preserve">053  720  7407 </t>
-        </is>
-      </c>
-      <c r="G899" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42028 </t>
-        </is>
-      </c>
-      <c r="H899" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260714</t>
-        </is>
-      </c>
-      <c r="I899" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대구광역시　수성구　달구벌대로　２４２１　（범어동）　２층　　　　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J899" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="900">
-      <c r="A900" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규    </t>
-        </is>
-      </c>
-      <c r="B900" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0508683</t>
-        </is>
-      </c>
-      <c r="C900" t="inlineStr">
-        <is>
-          <t xml:space="preserve">저축은행　　　　　　</t>
-        </is>
-      </c>
-      <c r="D900" t="inlineStr">
-        <is>
-          <t xml:space="preserve">참　　　　　경영전략팀　　　　</t>
-        </is>
-      </c>
-      <c r="E900" t="inlineStr">
-        <is>
-          <t xml:space="preserve">053  720  7300 </t>
-        </is>
-      </c>
-      <c r="F900" t="inlineStr">
-        <is>
-          <t xml:space="preserve">053  720  7400 </t>
-        </is>
-      </c>
-      <c r="G900" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42028 </t>
-        </is>
-      </c>
-      <c r="H900" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260714</t>
-        </is>
-      </c>
-      <c r="I900" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대구광역시　수성구　달구벌대로　２４２１　（범어동）　２층　　　　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J900" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="901">
-      <c r="A901" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규    </t>
-        </is>
-      </c>
-      <c r="B901" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0508696</t>
-        </is>
-      </c>
-      <c r="C901" t="inlineStr">
-        <is>
-          <t xml:space="preserve">저축은행　　　　　　</t>
-        </is>
-      </c>
-      <c r="D901" t="inlineStr">
-        <is>
-          <t xml:space="preserve">참　　　　　수신영업팀　　　　</t>
-        </is>
-      </c>
-      <c r="E901" t="inlineStr">
-        <is>
-          <t xml:space="preserve">053  720  7300 </t>
-        </is>
-      </c>
-      <c r="F901" t="inlineStr">
-        <is>
-          <t xml:space="preserve">053  720  7405 </t>
-        </is>
-      </c>
-      <c r="G901" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42028 </t>
-        </is>
-      </c>
-      <c r="H901" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260714</t>
-        </is>
-      </c>
-      <c r="I901" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대구광역시　수성구　달구벌대로　２４２１　（범어동）　２층　　　　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J901" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="902">
-      <c r="A902" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규    </t>
-        </is>
-      </c>
-      <c r="B902" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0508706</t>
-        </is>
-      </c>
-      <c r="C902" t="inlineStr">
-        <is>
-          <t xml:space="preserve">저축은행　　　　　　</t>
-        </is>
-      </c>
-      <c r="D902" t="inlineStr">
-        <is>
-          <t xml:space="preserve">참　　　　　기업금융１팀　　　</t>
-        </is>
-      </c>
-      <c r="E902" t="inlineStr">
-        <is>
-          <t xml:space="preserve">053  720  7300 </t>
-        </is>
-      </c>
-      <c r="F902" t="inlineStr">
-        <is>
-          <t xml:space="preserve">053  720  7402 </t>
-        </is>
-      </c>
-      <c r="G902" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42028 </t>
-        </is>
-      </c>
-      <c r="H902" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260714</t>
-        </is>
-      </c>
-      <c r="I902" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대구광역시　수성구　달구벌대로　２４２１　（범어동）　２층　　　　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J902" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="903">
-      <c r="A903" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규    </t>
-        </is>
-      </c>
-      <c r="B903" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0508719</t>
-        </is>
-      </c>
-      <c r="C903" t="inlineStr">
-        <is>
-          <t xml:space="preserve">저축은행　　　　　　</t>
-        </is>
-      </c>
-      <c r="D903" t="inlineStr">
-        <is>
-          <t xml:space="preserve">참　　　　　기업금융２팀　　　</t>
-        </is>
-      </c>
-      <c r="E903" t="inlineStr">
-        <is>
-          <t xml:space="preserve">053  720  7300 </t>
-        </is>
-      </c>
-      <c r="F903" t="inlineStr">
-        <is>
-          <t xml:space="preserve">053  720  7404 </t>
-        </is>
-      </c>
-      <c r="G903" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42028 </t>
-        </is>
-      </c>
-      <c r="H903" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260714</t>
-        </is>
-      </c>
-      <c r="I903" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대구광역시　수성구　달구벌대로　２４２１　（범어동）　２층　　　　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J903" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="904">
-      <c r="A904" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규    </t>
-        </is>
-      </c>
-      <c r="B904" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0508722</t>
-        </is>
-      </c>
-      <c r="C904" t="inlineStr">
-        <is>
-          <t xml:space="preserve">저축은행　　　　　　</t>
-        </is>
-      </c>
-      <c r="D904" t="inlineStr">
-        <is>
-          <t xml:space="preserve">참　　　　　여신관리팀　　　　</t>
-        </is>
-      </c>
-      <c r="E904" t="inlineStr">
-        <is>
-          <t xml:space="preserve">053  720  7300 </t>
-        </is>
-      </c>
-      <c r="F904" t="inlineStr">
-        <is>
-          <t xml:space="preserve">053  720  7402 </t>
-        </is>
-      </c>
-      <c r="G904" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42028 </t>
-        </is>
-      </c>
-      <c r="H904" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260714</t>
-        </is>
-      </c>
-      <c r="I904" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대구광역시　수성구　달구벌대로　２４２１　（범어동）　２층　　　　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J904" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>